--- a/InputData/ccs/BFoCPAbI/BAU Fraction of CCS Potential Achieved by Industry.xlsx
+++ b/InputData/ccs/BFoCPAbI/BAU Fraction of CCS Potential Achieved by Industry.xlsx
@@ -35884,4 +35884,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25E8880E-AF2E-48F4-A23A-B08EB814F290}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C87C9ED-B778-4193-A9C3-B7949AEFF542}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDA22ACB-0B36-444A-9EDB-569170CC84C9}"/>
 </file>
--- a/InputData/ccs/BFoCPAbI/BAU Fraction of CCS Potential Achieved by Industry.xlsx
+++ b/InputData/ccs/BFoCPAbI/BAU Fraction of CCS Potential Achieved by Industry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ccs\BFoCPAbI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\ccs\BFoCPAbI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CDD1C3-10D2-4809-BD59-1BCB02390B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF95468-C6F9-4ACC-A674-45EC18EADED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="3060" windowWidth="43200" windowHeight="17145" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -31631,124 +31631,94 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!B1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!B282</f>
         <v>0</v>
       </c>
       <c r="C10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!C1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!C282</f>
         <v>0</v>
       </c>
       <c r="D10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!D1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!D282</f>
         <v>0</v>
       </c>
       <c r="E10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!E1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!E282</f>
         <v>0</v>
       </c>
       <c r="F10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!F1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!F282</f>
         <v>0</v>
       </c>
       <c r="G10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!G1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!G282</f>
         <v>0</v>
       </c>
       <c r="H10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!H1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!H282</f>
         <v>0</v>
       </c>
       <c r="I10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!I1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!I282</f>
         <v>0</v>
       </c>
       <c r="J10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!J1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!J282</f>
         <v>0</v>
       </c>
       <c r="K10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!K1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!K282</f>
         <v>0</v>
       </c>
       <c r="L10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!L1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!L282</f>
-        <v>7.2509451221701132E-2</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!M1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!M282</f>
-        <v>0.14632284781067265</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!N1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!N282</f>
-        <v>0.22430075484895337</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!O1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!O282</f>
-        <v>0.30144254993781433</v>
-      </c>
-      <c r="P10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!P282</f>
-        <v>0.38143496250418402</v>
-      </c>
-      <c r="Q10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!Q282</f>
-        <v>0.38680033207566089</v>
-      </c>
-      <c r="R10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!R282</f>
-        <v>0.39213297034452449</v>
-      </c>
-      <c r="S10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!S282</f>
-        <v>0.39776118757096762</v>
-      </c>
-      <c r="T10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!T282</f>
-        <v>0.40116769069246927</v>
-      </c>
-      <c r="U10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!U282</f>
-        <v>0.40423294863096948</v>
-      </c>
-      <c r="V10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!V282</f>
-        <v>0.4066410742212464</v>
-      </c>
-      <c r="W10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!W282</f>
-        <v>0.40695687685312182</v>
-      </c>
-      <c r="X10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!X282</f>
-        <v>0.41190037995797696</v>
-      </c>
-      <c r="Y10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!Y282</f>
-        <v>0.41843989759215883</v>
-      </c>
-      <c r="Z10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!Z282</f>
-        <v>0.42562747195359713</v>
-      </c>
-      <c r="AA10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AA282</f>
-        <v>0.43504830369339176</v>
-      </c>
-      <c r="AB10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AB282</f>
-        <v>0.43798494442214675</v>
-      </c>
-      <c r="AC10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AC282</f>
-        <v>0.43361109650911933</v>
-      </c>
-      <c r="AD10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AD282</f>
-        <v>0.43598395826140429</v>
-      </c>
-      <c r="AE10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AE282</f>
-        <v>0.44217981007790547</v>
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
@@ -33579,125 +33549,95 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B6</f>
-        <v>0.21472747612426446</v>
-      </c>
-      <c r="C4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C6</f>
-        <v>0.21508482860112188</v>
-      </c>
-      <c r="D4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D6</f>
-        <v>0.22069008404254345</v>
-      </c>
-      <c r="E4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E6</f>
-        <v>0.21979339457147218</v>
-      </c>
-      <c r="F4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F6</f>
-        <v>0.22908344617435641</v>
-      </c>
-      <c r="G4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G6</f>
-        <v>0.23331697478668498</v>
-      </c>
-      <c r="H4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H6</f>
-        <v>0.23408573257966597</v>
-      </c>
-      <c r="I4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I6</f>
-        <v>0.23374166379457553</v>
-      </c>
-      <c r="J4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J6</f>
-        <v>0.23266612915727847</v>
-      </c>
-      <c r="K4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K6</f>
-        <v>0.23394199621627729</v>
-      </c>
-      <c r="L4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L6</f>
-        <v>0.23540239523069187</v>
-      </c>
-      <c r="M4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M6</f>
-        <v>0.23791103389500834</v>
-      </c>
-      <c r="N4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N6</f>
-        <v>0.23966354205254939</v>
-      </c>
-      <c r="O4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O6</f>
-        <v>0.23899126345235353</v>
-      </c>
-      <c r="P4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P6</f>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="Q4" s="38">
-        <f>P4</f>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="R4" s="38">
-        <f t="shared" ref="R4:AE4" si="0">Q4</f>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="S4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="T4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="U4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="V4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="W4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="X4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="Y4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="Z4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="AA4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="AB4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="AC4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="AD4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="AE4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
@@ -34179,125 +34119,95 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C12</f>
-        <v>1.7035952458279224E-2</v>
-      </c>
-      <c r="D10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D12</f>
-        <v>7.379540142338728E-2</v>
-      </c>
-      <c r="E10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E12</f>
-        <v>0.12978043460134511</v>
-      </c>
-      <c r="F10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F12</f>
-        <v>0.18340143676845078</v>
-      </c>
-      <c r="G10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G12</f>
-        <v>0.23726323944903455</v>
-      </c>
-      <c r="H10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H12</f>
-        <v>0.29179797708222832</v>
-      </c>
-      <c r="I10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I12</f>
-        <v>0.3465888690181968</v>
-      </c>
-      <c r="J10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J12</f>
-        <v>0.40293807245549862</v>
-      </c>
-      <c r="K10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K12</f>
-        <v>0.46127828033038998</v>
-      </c>
-      <c r="L10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L12</f>
-        <v>0.46428938925855379</v>
-      </c>
-      <c r="M10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M12</f>
-        <v>0.46892634931043969</v>
-      </c>
-      <c r="N10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N12</f>
-        <v>0.47908528156881697</v>
-      </c>
-      <c r="O10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O12</f>
-        <v>0.48916293796855054</v>
-      </c>
-      <c r="P10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P12</f>
-        <v>0.49657659767289786</v>
-      </c>
-      <c r="Q10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Q12</f>
-        <v>0.50296540850885785</v>
-      </c>
-      <c r="R10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!R12</f>
-        <v>0.51456524577321661</v>
-      </c>
-      <c r="S10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!S12</f>
-        <v>0.52416240494873922</v>
-      </c>
-      <c r="T10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!T12</f>
-        <v>0.5337411036527685</v>
-      </c>
-      <c r="U10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!U12</f>
-        <v>0.54446206562073074</v>
-      </c>
-      <c r="V10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!V12</f>
-        <v>0.55091923685396671</v>
-      </c>
-      <c r="W10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!W12</f>
-        <v>0.55490684703794002</v>
-      </c>
-      <c r="X10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!X12</f>
-        <v>0.5637005765733456</v>
-      </c>
-      <c r="Y10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Y12</f>
-        <v>0.56928750459812449</v>
-      </c>
-      <c r="Z10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Z12</f>
-        <v>0.57880294177833458</v>
-      </c>
-      <c r="AA10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AA12</f>
-        <v>0.58666244942241519</v>
-      </c>
-      <c r="AB10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AB12</f>
-        <v>0.60164854466283457</v>
-      </c>
-      <c r="AC10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AC12</f>
-        <v>0.61282270980178088</v>
-      </c>
-      <c r="AD10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AD12</f>
-        <v>0.61033926350690149</v>
-      </c>
-      <c r="AE10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AE12</f>
-        <v>0.61297940852101807</v>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
@@ -34589,250 +34499,190 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B16</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C16</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D16</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E16</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F16</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G16</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H16</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I16</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J16</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K16</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L16</f>
-        <v>0.12584183275816249</v>
-      </c>
-      <c r="M14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M16</f>
-        <v>0.24902718409452954</v>
-      </c>
-      <c r="N14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N16</f>
-        <v>0.37063322693604867</v>
-      </c>
-      <c r="O14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O16</f>
-        <v>0.49229651422155546</v>
-      </c>
-      <c r="P14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P16</f>
-        <v>0.61089208806394202</v>
-      </c>
-      <c r="Q14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Q16</f>
-        <v>0.60113262212048835</v>
-      </c>
-      <c r="R14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!R16</f>
-        <v>0.59361131092300634</v>
-      </c>
-      <c r="S14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!S16</f>
-        <v>0.58777591828937059</v>
-      </c>
-      <c r="T14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!T16</f>
-        <v>0.58158880336000873</v>
-      </c>
-      <c r="U14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!U16</f>
-        <v>0.57705234918255754</v>
-      </c>
-      <c r="V14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!V16</f>
-        <v>0.57101307812884161</v>
-      </c>
-      <c r="W14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!W16</f>
-        <v>0.56378506448164112</v>
-      </c>
-      <c r="X14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!X16</f>
-        <v>0.55816163289218235</v>
-      </c>
-      <c r="Y14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Y16</f>
-        <v>0.55553315123035074</v>
-      </c>
-      <c r="Z14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Z16</f>
-        <v>0.54979518443341302</v>
-      </c>
-      <c r="AA14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AA16</f>
-        <v>0.54349694548834093</v>
-      </c>
-      <c r="AB14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AB16</f>
-        <v>0.53853472784908896</v>
-      </c>
-      <c r="AC14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AC16</f>
-        <v>0.53346663031249886</v>
-      </c>
-      <c r="AD14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AD16</f>
-        <v>0.52939041470186365</v>
-      </c>
-      <c r="AE14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AE16</f>
-        <v>0.52524957511634962</v>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B17</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C17</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D17</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E17</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F17</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G17</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H17</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I17</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J17</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K17</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L17</f>
-        <v>5.9126788165476771E-2</v>
-      </c>
-      <c r="M15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M17</f>
-        <v>0.11856907216886765</v>
-      </c>
-      <c r="N15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N17</f>
-        <v>0.17576472359261788</v>
-      </c>
-      <c r="O15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O17</f>
-        <v>0.23485961304457414</v>
-      </c>
-      <c r="P15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P17</f>
-        <v>0.29224072486387437</v>
-      </c>
-      <c r="Q15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Q17</f>
-        <v>0.29029708108805763</v>
-      </c>
-      <c r="R15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!R17</f>
-        <v>0.28995271918878357</v>
-      </c>
-      <c r="S15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!S17</f>
-        <v>0.28715947165900441</v>
-      </c>
-      <c r="T15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!T17</f>
-        <v>0.28468453561162887</v>
-      </c>
-      <c r="U15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!U17</f>
-        <v>0.28501649052722078</v>
-      </c>
-      <c r="V15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!V17</f>
-        <v>0.28310185577501101</v>
-      </c>
-      <c r="W15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!W17</f>
-        <v>0.27877525350837651</v>
-      </c>
-      <c r="X15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!X17</f>
-        <v>0.27669248616271735</v>
-      </c>
-      <c r="Y15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Y17</f>
-        <v>0.27625468159600419</v>
-      </c>
-      <c r="Z15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Z17</f>
-        <v>0.27769841203833734</v>
-      </c>
-      <c r="AA15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AA17</f>
-        <v>0.27960437231313717</v>
-      </c>
-      <c r="AB15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AB17</f>
-        <v>0.28037410217497655</v>
-      </c>
-      <c r="AC15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AC17</f>
-        <v>0.28011705509528367</v>
-      </c>
-      <c r="AD15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AD17</f>
-        <v>0.27826746616136672</v>
-      </c>
-      <c r="AE15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AE17</f>
-        <v>0.27732033387354721</v>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
@@ -35887,6 +35737,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -36030,29 +35895,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25E8880E-AF2E-48F4-A23A-B08EB814F290}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDA22ACB-0B36-444A-9EDB-569170CC84C9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C87C9ED-B778-4193-A9C3-B7949AEFF542}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C87C9ED-B778-4193-A9C3-B7949AEFF542}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDA22ACB-0B36-444A-9EDB-569170CC84C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25E8880E-AF2E-48F4-A23A-B08EB814F290}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/ccs/BFoCPAbI/BAU Fraction of CCS Potential Achieved by Industry.xlsx
+++ b/InputData/ccs/BFoCPAbI/BAU Fraction of CCS Potential Achieved by Industry.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\ccs\BFoCPAbI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\administer\Dropbox\kjh\2025\02. EPS\EI\251020_메일회신\회신용 파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF95468-C6F9-4ACC-A674-45EC18EADED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2460D45A-65CA-40F5-91ED-5B2A573F9111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="3060" windowWidth="43200" windowHeight="17145" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="458">
   <si>
     <t>Notes</t>
   </si>
@@ -1398,6 +1398,58 @@
   </si>
   <si>
     <t>Industrial Sector Energy Related Emissions before CCS[hydrogen if,construction 41T43,CO2] : test</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">As of 2025, South Korea's Carbon Capture and Storage (CCS) technology has not yet reached the mass commercialization stage. It is determined that there are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>significant practical uncertainties regarding R&amp;D progress and the securement of storage sites.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Therefore, to enhance the realism of the simulation, we will </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>use the latest CCS-related data from the United States</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> instead of Korean data to set the initial modeling parameters.</t>
+    </r>
+  </si>
+  <si>
+    <t>South Korea Context</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.plan15.org/press/?bmode=view&amp;idx=161107222&amp;utm_source=chatgpt.com</t>
   </si>
 </sst>
 </file>
@@ -1405,14 +1457,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1420,7 +1472,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1428,14 +1480,14 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1443,8 +1495,32 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1586,11 +1662,11 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1640,17 +1716,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="백분율" xfId="1" builtinId="5"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2050,21 +2128,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="103.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="103.375" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="5" max="5" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -2072,75 +2150,75 @@
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="8">
         <v>2023</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="10" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" s="8">
         <v>2022</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" s="37" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B17" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B19" s="8">
         <v>2019</v>
       </c>
@@ -2148,71 +2226,92 @@
       <c r="D19" s="3"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B23" s="8"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
       <c r="B30" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>174</v>
       </c>
     </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="40" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="39" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="39" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>457</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B21" r:id="rId1" xr:uid="{662160B2-7C08-4070-B1C1-944156B986F3}"/>
     <hyperlink ref="B14" r:id="rId2" xr:uid="{9E6AC009-89C4-485D-AF2A-960A1B40FA39}"/>
@@ -2225,20 +2324,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9816DDC5-B47D-412D-83A1-985DCFECCE82}">
   <dimension ref="A1:I48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.7109375" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="27.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
-    <col min="8" max="8" width="37.28515625" customWidth="1"/>
-    <col min="9" max="9" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="47.75" customWidth="1"/>
+    <col min="2" max="2" width="25.75" customWidth="1"/>
+    <col min="3" max="3" width="18.875" customWidth="1"/>
+    <col min="4" max="4" width="27.875" customWidth="1"/>
+    <col min="5" max="5" width="12.125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="30.125" customWidth="1"/>
+    <col min="7" max="7" width="26.25" customWidth="1"/>
+    <col min="8" max="8" width="37.25" customWidth="1"/>
+    <col min="9" max="9" width="31.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>115</v>
       </c>
@@ -2251,7 +2350,7 @@
       <c r="H1" s="20"/>
       <c r="I1" s="20"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>114</v>
       </c>
@@ -2280,7 +2379,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>106</v>
       </c>
@@ -2303,7 +2402,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -2323,7 +2422,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -2346,7 +2445,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>103</v>
       </c>
@@ -2369,7 +2468,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -2395,7 +2494,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>99</v>
       </c>
@@ -2418,7 +2517,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>98</v>
       </c>
@@ -2438,7 +2537,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>97</v>
       </c>
@@ -2461,7 +2560,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>95</v>
       </c>
@@ -2481,7 +2580,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="99" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -2507,7 +2606,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -2527,7 +2626,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -2547,7 +2646,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -2573,7 +2672,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>85</v>
       </c>
@@ -2596,7 +2695,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -2622,7 +2721,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -2648,7 +2747,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -2671,7 +2770,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>77</v>
       </c>
@@ -2694,7 +2793,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>75</v>
       </c>
@@ -2720,7 +2819,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -2740,7 +2839,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -2766,7 +2865,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -2789,7 +2888,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -2809,7 +2908,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2832,7 +2931,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -2855,7 +2954,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -2878,7 +2977,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -2898,7 +2997,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>53</v>
       </c>
@@ -2924,13 +3023,13 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B34" s="15"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -2939,7 +3038,7 @@
         <v>28.360000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -2948,13 +3047,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B39" s="13"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -2967,7 +3066,7 @@
         <v>0.6921272158498436</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -2980,7 +3079,7 @@
         <v>4.6923879040667367E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -2993,7 +3092,7 @@
         <v>7.8206465067778938E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -3006,7 +3105,7 @@
         <v>5.7351407716371226E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -3019,7 +3118,7 @@
         <v>3.6496350364963501E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -3032,7 +3131,7 @@
         <v>2.0855057351407719E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -3045,7 +3144,7 @@
         <v>3.6235662148070912E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>36</v>
       </c>
@@ -3058,7 +3157,7 @@
         <v>5.7351407716371219E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>35</v>
       </c>
@@ -3072,6 +3171,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I7" r:id="rId1" xr:uid="{94071961-1291-4DF9-80E2-B3C8671FAEDD}"/>
     <hyperlink ref="I18" r:id="rId2" xr:uid="{40963785-0F41-42BB-84A5-A85D09A42630}"/>
@@ -3088,30 +3188,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED05A5AB-C865-4DF5-BD35-041C1CC241DD}">
   <dimension ref="A1:H48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.125" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="10.375" customWidth="1"/>
+    <col min="4" max="4" width="20.25" customWidth="1"/>
+    <col min="5" max="5" width="19.625" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="17.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>151</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2000</v>
       </c>
@@ -3119,7 +3219,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2015</v>
       </c>
@@ -3127,7 +3227,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2020</v>
       </c>
@@ -3138,7 +3238,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -3149,19 +3249,19 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>149</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="36" t="s">
         <v>147</v>
       </c>
@@ -3172,7 +3272,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>0.56999999999999995</v>
       </c>
@@ -3184,7 +3284,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>0.34</v>
       </c>
@@ -3196,7 +3296,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>0.03</v>
       </c>
@@ -3208,7 +3308,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>0.03</v>
       </c>
@@ -3220,7 +3320,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>0.02</v>
       </c>
@@ -3232,7 +3332,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>0.04</v>
       </c>
@@ -3244,49 +3344,49 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B18" s="5"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="34" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>136</v>
       </c>
       <c r="B24" s="5"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>70</v>
       </c>
@@ -3294,12 +3394,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>80</v>
       </c>
@@ -3307,12 +3407,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <f>B5*B12</f>
         <v>82.524271844660205</v>
@@ -3321,8 +3421,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>128</v>
       </c>
@@ -3333,7 +3433,7 @@
       <c r="F33" s="32"/>
       <c r="G33" s="31"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="28"/>
       <c r="B34" s="29" t="s">
         <v>127</v>
@@ -3357,7 +3457,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="28" t="s">
         <v>121</v>
       </c>
@@ -3388,7 +3488,7 @@
         <v>167.47572815533979</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="28" t="s">
         <v>120</v>
       </c>
@@ -3417,7 +3517,7 @@
         <v>33.486929491831802</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="26" t="s">
         <v>119</v>
       </c>
@@ -3445,43 +3545,44 @@
         <v>57.76699029126214</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C38" s="2"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <f>'Operational Capacity'!B35</f>
         <v>28.360000000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="12">
         <f>C36/A42</f>
         <v>0.87296479384337322</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <f>A45*'Operational Capacity'!B36</f>
         <v>8.7296479384337324</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3489,12 +3590,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{000817FC-5CAD-42B5-92F8-1A675198574D}">
   <dimension ref="A25:H54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" customWidth="1"/>
+    <col min="1" max="1" width="48.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>171</v>
       </c>
@@ -3506,7 +3607,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>2022</v>
       </c>
@@ -3517,17 +3618,17 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -3541,32 +3642,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>175</v>
       </c>
@@ -3583,7 +3684,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>176</v>
       </c>
@@ -3600,7 +3701,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -3608,17 +3709,17 @@
         <v>177</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -3632,7 +3733,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -3646,62 +3747,62 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>122</v>
       </c>
@@ -3718,6 +3819,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -3727,17 +3829,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D869D793-4D45-441A-BEF3-5973BA28AC13}">
   <dimension ref="A1:AE300"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="80.140625" customWidth="1"/>
+    <col min="1" max="1" width="80.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>172</v>
       </c>
@@ -3832,7 +3934,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>179</v>
       </c>
@@ -3927,7 +4029,7 @@
         <v>9716000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>180</v>
       </c>
@@ -4022,7 +4124,7 @@
         <v>665338000000</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>181</v>
       </c>
@@ -4117,7 +4219,7 @@
         <v>69366600000000</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>182</v>
       </c>
@@ -4212,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>183</v>
       </c>
@@ -4307,7 +4409,7 @@
         <v>6699000000000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>184</v>
       </c>
@@ -4402,7 +4504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>185</v>
       </c>
@@ -4497,7 +4599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>186</v>
       </c>
@@ -4592,7 +4694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>187</v>
       </c>
@@ -4687,7 +4789,7 @@
         <v>75479100000000</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>188</v>
       </c>
@@ -4782,7 +4884,7 @@
         <v>160400000000000</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>189</v>
       </c>
@@ -4877,7 +4979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>190</v>
       </c>
@@ -4972,7 +5074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>191</v>
       </c>
@@ -5067,7 +5169,7 @@
         <v>83100000000000</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>192</v>
       </c>
@@ -5162,7 +5264,7 @@
         <v>44070000000000</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>193</v>
       </c>
@@ -5257,7 +5359,7 @@
         <v>5642000000000</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>194</v>
       </c>
@@ -5352,7 +5454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>195</v>
       </c>
@@ -5447,7 +5549,7 @@
         <v>546600000000</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>196</v>
       </c>
@@ -5542,7 +5644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>197</v>
       </c>
@@ -5637,7 +5739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>198</v>
       </c>
@@ -5732,7 +5834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>199</v>
       </c>
@@ -5827,7 +5929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>200</v>
       </c>
@@ -5922,7 +6024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>201</v>
       </c>
@@ -6017,7 +6119,7 @@
         <v>1400230000000</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>202</v>
       </c>
@@ -6112,7 +6214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>203</v>
       </c>
@@ -6207,7 +6309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B29" s="38"/>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -6239,7 +6341,7 @@
       <c r="AD29" s="38"/>
       <c r="AE29" s="38"/>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>172</v>
       </c>
@@ -6334,7 +6436,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>204</v>
       </c>
@@ -6429,7 +6531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>205</v>
       </c>
@@ -6524,7 +6626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>206</v>
       </c>
@@ -6619,7 +6721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>207</v>
       </c>
@@ -6714,7 +6816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>208</v>
       </c>
@@ -6809,7 +6911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>209</v>
       </c>
@@ -6904,7 +7006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>210</v>
       </c>
@@ -6999,7 +7101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>211</v>
       </c>
@@ -7094,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>212</v>
       </c>
@@ -7189,7 +7291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>213</v>
       </c>
@@ -7284,7 +7386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>214</v>
       </c>
@@ -7379,7 +7481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>215</v>
       </c>
@@ -7474,7 +7576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>216</v>
       </c>
@@ -7569,7 +7671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>217</v>
       </c>
@@ -7664,7 +7766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>218</v>
       </c>
@@ -7759,7 +7861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>219</v>
       </c>
@@ -7854,7 +7956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>220</v>
       </c>
@@ -7949,7 +8051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>221</v>
       </c>
@@ -8044,7 +8146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>222</v>
       </c>
@@ -8139,7 +8241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>223</v>
       </c>
@@ -8234,7 +8336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>224</v>
       </c>
@@ -8329,7 +8431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>225</v>
       </c>
@@ -8424,7 +8526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>226</v>
       </c>
@@ -8519,7 +8621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>227</v>
       </c>
@@ -8614,7 +8716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>228</v>
       </c>
@@ -8709,7 +8811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>229</v>
       </c>
@@ -8804,7 +8906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -8899,7 +9001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>231</v>
       </c>
@@ -8994,7 +9096,7 @@
         <v>11727400000</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>232</v>
       </c>
@@ -9089,7 +9191,7 @@
         <v>867461000000</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>233</v>
       </c>
@@ -9184,7 +9286,7 @@
         <v>13310600000000</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>234</v>
       </c>
@@ -9279,7 +9381,7 @@
         <v>479409000000</v>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>235</v>
       </c>
@@ -9374,7 +9476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>236</v>
       </c>
@@ -9469,7 +9571,7 @@
         <v>1238280000000</v>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>237</v>
       </c>
@@ -9564,7 +9666,7 @@
         <v>1923620000000</v>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>238</v>
       </c>
@@ -9659,7 +9761,7 @@
         <v>5779600000000</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>239</v>
       </c>
@@ -9754,7 +9856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>240</v>
       </c>
@@ -9849,7 +9951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>241</v>
       </c>
@@ -9944,7 +10046,7 @@
         <v>4095420000000</v>
       </c>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>242</v>
       </c>
@@ -10039,7 +10141,7 @@
         <v>5339520000000</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>243</v>
       </c>
@@ -10134,7 +10236,7 @@
         <v>410773000000</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>244</v>
       </c>
@@ -10229,7 +10331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>245</v>
       </c>
@@ -10324,7 +10426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>246</v>
       </c>
@@ -10419,7 +10521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>247</v>
       </c>
@@ -10514,7 +10616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>248</v>
       </c>
@@ -10609,7 +10711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>249</v>
       </c>
@@ -10704,7 +10806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>250</v>
       </c>
@@ -10799,7 +10901,7 @@
         <v>1496730000000</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>251</v>
       </c>
@@ -10894,7 +10996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>252</v>
       </c>
@@ -10989,7 +11091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>253</v>
       </c>
@@ -11084,7 +11186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>254</v>
       </c>
@@ -11179,7 +11281,7 @@
         <v>6462710000000</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>255</v>
       </c>
@@ -11274,7 +11376,7 @@
         <v>109816000000</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>256</v>
       </c>
@@ -11369,7 +11471,7 @@
         <v>155700000000000</v>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>257</v>
       </c>
@@ -11464,7 +11566,7 @@
         <v>9168770000000</v>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>258</v>
       </c>
@@ -11559,7 +11661,7 @@
         <v>46034900000000</v>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>259</v>
       </c>
@@ -11654,7 +11756,7 @@
         <v>6696170000000</v>
       </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>260</v>
       </c>
@@ -11749,7 +11851,7 @@
         <v>2512390000000</v>
       </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>261</v>
       </c>
@@ -11844,7 +11946,7 @@
         <v>22099500000000</v>
       </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>262</v>
       </c>
@@ -11939,7 +12041,7 @@
         <v>21011700000000</v>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>263</v>
       </c>
@@ -12034,7 +12136,7 @@
         <v>146795000000000</v>
       </c>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>264</v>
       </c>
@@ -12129,7 +12231,7 @@
         <v>5682730000000</v>
       </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>265</v>
       </c>
@@ -12224,7 +12326,7 @@
         <v>4059090000000</v>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>266</v>
       </c>
@@ -12319,7 +12421,7 @@
         <v>10214100000000</v>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>267</v>
       </c>
@@ -12414,7 +12516,7 @@
         <v>18213300000000</v>
       </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>268</v>
       </c>
@@ -12509,7 +12611,7 @@
         <v>11625400000000</v>
       </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>269</v>
       </c>
@@ -12604,7 +12706,7 @@
         <v>7104730000000</v>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>270</v>
       </c>
@@ -12699,7 +12801,7 @@
         <v>1530250000000</v>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>271</v>
       </c>
@@ -12794,7 +12896,7 @@
         <v>2385050000000</v>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>272</v>
       </c>
@@ -12889,7 +12991,7 @@
         <v>3633550000000</v>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>273</v>
       </c>
@@ -12984,7 +13086,7 @@
         <v>6717400000000</v>
       </c>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>274</v>
       </c>
@@ -13079,7 +13181,7 @@
         <v>3802810000000</v>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>275</v>
       </c>
@@ -13174,7 +13276,7 @@
         <v>20910900000000</v>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>276</v>
       </c>
@@ -13269,7 +13371,7 @@
         <v>41048000000000</v>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>277</v>
       </c>
@@ -13364,7 +13466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>278</v>
       </c>
@@ -13459,7 +13561,7 @@
         <v>10394500000000</v>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>279</v>
       </c>
@@ -13554,7 +13656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>280</v>
       </c>
@@ -13649,7 +13751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>281</v>
       </c>
@@ -13744,7 +13846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>282</v>
       </c>
@@ -13839,7 +13941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>283</v>
       </c>
@@ -13934,7 +14036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>284</v>
       </c>
@@ -14029,7 +14131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>285</v>
       </c>
@@ -14124,7 +14226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>286</v>
       </c>
@@ -14219,7 +14321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>287</v>
       </c>
@@ -14314,7 +14416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>288</v>
       </c>
@@ -14409,7 +14511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>289</v>
       </c>
@@ -14504,7 +14606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>290</v>
       </c>
@@ -14599,7 +14701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>291</v>
       </c>
@@ -14694,7 +14796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>292</v>
       </c>
@@ -14789,7 +14891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>293</v>
       </c>
@@ -14884,7 +14986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>294</v>
       </c>
@@ -14979,7 +15081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>295</v>
       </c>
@@ -15074,7 +15176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>296</v>
       </c>
@@ -15169,7 +15271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>297</v>
       </c>
@@ -15264,7 +15366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>298</v>
       </c>
@@ -15359,7 +15461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>299</v>
       </c>
@@ -15454,7 +15556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>300</v>
       </c>
@@ -15549,7 +15651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>301</v>
       </c>
@@ -15644,7 +15746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>302</v>
       </c>
@@ -15739,7 +15841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>303</v>
       </c>
@@ -15834,7 +15936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>304</v>
       </c>
@@ -15929,7 +16031,7 @@
         <v>47012600000000</v>
       </c>
     </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>305</v>
       </c>
@@ -16024,7 +16126,7 @@
         <v>560345000000</v>
       </c>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>306</v>
       </c>
@@ -16119,7 +16221,7 @@
         <v>9549060000000</v>
       </c>
     </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>307</v>
       </c>
@@ -16214,7 +16316,7 @@
         <v>6406920000000</v>
       </c>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>308</v>
       </c>
@@ -16309,7 +16411,7 @@
         <v>967266000000</v>
       </c>
     </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>309</v>
       </c>
@@ -16404,7 +16506,7 @@
         <v>358391000000</v>
       </c>
     </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>310</v>
       </c>
@@ -16499,7 +16601,7 @@
         <v>548392000000</v>
       </c>
     </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>311</v>
       </c>
@@ -16594,7 +16696,7 @@
         <v>739519000000</v>
       </c>
     </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>312</v>
       </c>
@@ -16689,7 +16791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>313</v>
       </c>
@@ -16784,7 +16886,7 @@
         <v>71258000000</v>
       </c>
     </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>314</v>
       </c>
@@ -16879,7 +16981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>315</v>
       </c>
@@ -16974,7 +17076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>316</v>
       </c>
@@ -17069,7 +17171,7 @@
         <v>4134700000000</v>
       </c>
     </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>317</v>
       </c>
@@ -17164,7 +17266,7 @@
         <v>202683000000</v>
       </c>
     </row>
-    <row r="145" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>318</v>
       </c>
@@ -17259,7 +17361,7 @@
         <v>362743000000</v>
       </c>
     </row>
-    <row r="146" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>319</v>
       </c>
@@ -17354,7 +17456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>320</v>
       </c>
@@ -17449,7 +17551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>321</v>
       </c>
@@ -17544,7 +17646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>322</v>
       </c>
@@ -17639,7 +17741,7 @@
         <v>105131000000</v>
       </c>
     </row>
-    <row r="150" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>323</v>
       </c>
@@ -17734,7 +17836,7 @@
         <v>174318000000</v>
       </c>
     </row>
-    <row r="151" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>324</v>
       </c>
@@ -17829,7 +17931,7 @@
         <v>98602600000</v>
       </c>
     </row>
-    <row r="152" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>325</v>
       </c>
@@ -17924,7 +18026,7 @@
         <v>1119600000000</v>
       </c>
     </row>
-    <row r="153" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>326</v>
       </c>
@@ -18019,7 +18121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>327</v>
       </c>
@@ -18114,7 +18216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>328</v>
       </c>
@@ -18209,7 +18311,7 @@
         <v>42095300000000</v>
       </c>
     </row>
-    <row r="156" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>329</v>
       </c>
@@ -18304,7 +18406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>330</v>
       </c>
@@ -18399,7 +18501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>331</v>
       </c>
@@ -18494,7 +18596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>332</v>
       </c>
@@ -18589,7 +18691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>333</v>
       </c>
@@ -18684,7 +18786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>334</v>
       </c>
@@ -18779,7 +18881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>335</v>
       </c>
@@ -18874,7 +18976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>336</v>
       </c>
@@ -18969,7 +19071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>337</v>
       </c>
@@ -19064,7 +19166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>338</v>
       </c>
@@ -19159,7 +19261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>339</v>
       </c>
@@ -19254,7 +19356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>340</v>
       </c>
@@ -19349,7 +19451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>341</v>
       </c>
@@ -19444,7 +19546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>342</v>
       </c>
@@ -19539,7 +19641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>343</v>
       </c>
@@ -19634,7 +19736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>344</v>
       </c>
@@ -19729,7 +19831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>345</v>
       </c>
@@ -19824,7 +19926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>346</v>
       </c>
@@ -19919,7 +20021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>347</v>
       </c>
@@ -20014,7 +20116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>348</v>
       </c>
@@ -20109,7 +20211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>349</v>
       </c>
@@ -20204,7 +20306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>350</v>
       </c>
@@ -20299,7 +20401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>351</v>
       </c>
@@ -20394,7 +20496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>352</v>
       </c>
@@ -20489,7 +20591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>353</v>
       </c>
@@ -20584,7 +20686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>354</v>
       </c>
@@ -20679,7 +20781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>355</v>
       </c>
@@ -20774,7 +20876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>356</v>
       </c>
@@ -20869,7 +20971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>357</v>
       </c>
@@ -20964,7 +21066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>358</v>
       </c>
@@ -21059,7 +21161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>359</v>
       </c>
@@ -21154,7 +21256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>360</v>
       </c>
@@ -21249,7 +21351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>361</v>
       </c>
@@ -21344,7 +21446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>362</v>
       </c>
@@ -21439,7 +21541,7 @@
         <v>95518500000000</v>
       </c>
     </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>363</v>
       </c>
@@ -21534,7 +21636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>364</v>
       </c>
@@ -21629,7 +21731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>365</v>
       </c>
@@ -21724,7 +21826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>366</v>
       </c>
@@ -21819,7 +21921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>367</v>
       </c>
@@ -21914,7 +22016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>368</v>
       </c>
@@ -22009,7 +22111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>369</v>
       </c>
@@ -22104,7 +22206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>370</v>
       </c>
@@ -22199,7 +22301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>371</v>
       </c>
@@ -22294,7 +22396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>372</v>
       </c>
@@ -22389,7 +22491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>373</v>
       </c>
@@ -22484,7 +22586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>374</v>
       </c>
@@ -22579,7 +22681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>375</v>
       </c>
@@ -22674,7 +22776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>376</v>
       </c>
@@ -22769,7 +22871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>377</v>
       </c>
@@ -22864,7 +22966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>378</v>
       </c>
@@ -22959,7 +23061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>379</v>
       </c>
@@ -23054,7 +23156,7 @@
         <v>2398450000</v>
       </c>
     </row>
-    <row r="207" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>380</v>
       </c>
@@ -23149,7 +23251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>381</v>
       </c>
@@ -23244,7 +23346,7 @@
         <v>338570000000</v>
       </c>
     </row>
-    <row r="209" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>382</v>
       </c>
@@ -23339,7 +23441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>383</v>
       </c>
@@ -23434,7 +23536,7 @@
         <v>21469000000</v>
       </c>
     </row>
-    <row r="211" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>384</v>
       </c>
@@ -23529,7 +23631,7 @@
         <v>10838400000</v>
       </c>
     </row>
-    <row r="212" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>385</v>
       </c>
@@ -23624,7 +23726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>386</v>
       </c>
@@ -23719,7 +23821,7 @@
         <v>1880500000000</v>
       </c>
     </row>
-    <row r="214" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>387</v>
       </c>
@@ -23814,7 +23916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>388</v>
       </c>
@@ -23909,7 +24011,7 @@
         <v>153739000000</v>
       </c>
     </row>
-    <row r="216" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>389</v>
       </c>
@@ -24004,7 +24106,7 @@
         <v>161615000</v>
       </c>
     </row>
-    <row r="217" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>390</v>
       </c>
@@ -24099,7 +24201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>391</v>
       </c>
@@ -24194,7 +24296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>392</v>
       </c>
@@ -24289,7 +24391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>393</v>
       </c>
@@ -24384,7 +24486,7 @@
         <v>9287170000</v>
       </c>
     </row>
-    <row r="221" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>394</v>
       </c>
@@ -24479,7 +24581,7 @@
         <v>517514</v>
       </c>
     </row>
-    <row r="222" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>395</v>
       </c>
@@ -24574,7 +24676,7 @@
         <v>2222210</v>
       </c>
     </row>
-    <row r="223" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>396</v>
       </c>
@@ -24669,7 +24771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>397</v>
       </c>
@@ -24764,7 +24866,7 @@
         <v>83436100</v>
       </c>
     </row>
-    <row r="225" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>398</v>
       </c>
@@ -24859,7 +24961,7 @@
         <v>46787300000</v>
       </c>
     </row>
-    <row r="226" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>399</v>
       </c>
@@ -24954,7 +25056,7 @@
         <v>26480300000</v>
       </c>
     </row>
-    <row r="227" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>400</v>
       </c>
@@ -25049,7 +25151,7 @@
         <v>33843400000</v>
       </c>
     </row>
-    <row r="228" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>401</v>
       </c>
@@ -25144,7 +25246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>402</v>
       </c>
@@ -25239,7 +25341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>403</v>
       </c>
@@ -25334,7 +25436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>404</v>
       </c>
@@ -25429,7 +25531,7 @@
         <v>6034760000000</v>
       </c>
     </row>
-    <row r="232" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>405</v>
       </c>
@@ -25524,7 +25626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>406</v>
       </c>
@@ -25619,7 +25721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>407</v>
       </c>
@@ -25714,7 +25816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>408</v>
       </c>
@@ -25809,7 +25911,7 @@
         <v>242521000000</v>
       </c>
     </row>
-    <row r="236" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>409</v>
       </c>
@@ -25904,7 +26006,7 @@
         <v>107125000000</v>
       </c>
     </row>
-    <row r="237" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>410</v>
       </c>
@@ -25999,7 +26101,7 @@
         <v>184319000000</v>
       </c>
     </row>
-    <row r="238" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>411</v>
       </c>
@@ -26094,7 +26196,7 @@
         <v>136687000000</v>
       </c>
     </row>
-    <row r="239" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>412</v>
       </c>
@@ -26189,7 +26291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>413</v>
       </c>
@@ -26284,7 +26386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>414</v>
       </c>
@@ -26379,7 +26481,7 @@
         <v>98336000000</v>
       </c>
     </row>
-    <row r="242" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>415</v>
       </c>
@@ -26474,7 +26576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>416</v>
       </c>
@@ -26569,7 +26671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>417</v>
       </c>
@@ -26664,7 +26766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>418</v>
       </c>
@@ -26759,7 +26861,7 @@
         <v>91821200000</v>
       </c>
     </row>
-    <row r="246" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>419</v>
       </c>
@@ -26854,7 +26956,7 @@
         <v>137978000000</v>
       </c>
     </row>
-    <row r="247" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>420</v>
       </c>
@@ -26949,7 +27051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>421</v>
       </c>
@@ -27044,7 +27146,7 @@
         <v>66376800000</v>
       </c>
     </row>
-    <row r="249" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>422</v>
       </c>
@@ -27139,7 +27241,7 @@
         <v>70556100000</v>
       </c>
     </row>
-    <row r="250" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>423</v>
       </c>
@@ -27234,7 +27336,7 @@
         <v>71170700000</v>
       </c>
     </row>
-    <row r="251" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>424</v>
       </c>
@@ -27329,7 +27431,7 @@
         <v>40293200000</v>
       </c>
     </row>
-    <row r="252" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>425</v>
       </c>
@@ -27424,7 +27526,7 @@
         <v>334588000000</v>
       </c>
     </row>
-    <row r="253" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>426</v>
       </c>
@@ -27519,7 +27621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>427</v>
       </c>
@@ -27614,7 +27716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>428</v>
       </c>
@@ -27709,7 +27811,7 @@
         <v>2105620000000</v>
       </c>
     </row>
-    <row r="256" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>429</v>
       </c>
@@ -27804,7 +27906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>430</v>
       </c>
@@ -27899,7 +28001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>431</v>
       </c>
@@ -27994,7 +28096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>432</v>
       </c>
@@ -28089,7 +28191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>433</v>
       </c>
@@ -28184,7 +28286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>434</v>
       </c>
@@ -28279,7 +28381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>435</v>
       </c>
@@ -28374,7 +28476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>436</v>
       </c>
@@ -28469,7 +28571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>437</v>
       </c>
@@ -28564,7 +28666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>438</v>
       </c>
@@ -28659,7 +28761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>439</v>
       </c>
@@ -28754,7 +28856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>440</v>
       </c>
@@ -28849,7 +28951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>441</v>
       </c>
@@ -28944,7 +29046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>442</v>
       </c>
@@ -29039,7 +29141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>443</v>
       </c>
@@ -29134,7 +29236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>444</v>
       </c>
@@ -29229,7 +29331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>445</v>
       </c>
@@ -29324,7 +29426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>446</v>
       </c>
@@ -29419,7 +29521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>447</v>
       </c>
@@ -29514,7 +29616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>448</v>
       </c>
@@ -29609,7 +29711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>449</v>
       </c>
@@ -29704,7 +29806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>450</v>
       </c>
@@ -29799,7 +29901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>451</v>
       </c>
@@ -29894,7 +29996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>452</v>
       </c>
@@ -29989,7 +30091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>453</v>
       </c>
@@ -30084,7 +30186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B281" s="38"/>
       <c r="C281" s="38"/>
       <c r="D281" s="38"/>
@@ -30116,7 +30218,7 @@
       <c r="AD281" s="38"/>
       <c r="AE281" s="38"/>
     </row>
-    <row r="282" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>167</v>
       </c>
@@ -30241,7 +30343,7 @@
         <v>118453820000000</v>
       </c>
     </row>
-    <row r="283" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B283" s="38"/>
       <c r="C283" s="38"/>
       <c r="D283" s="38"/>
@@ -30273,7 +30375,7 @@
       <c r="AD283" s="38"/>
       <c r="AE283" s="38"/>
     </row>
-    <row r="284" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B284" s="38"/>
       <c r="C284" s="38"/>
       <c r="D284" s="38"/>
@@ -30305,7 +30407,7 @@
       <c r="AD284" s="38"/>
       <c r="AE284" s="38"/>
     </row>
-    <row r="285" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B285" s="38"/>
       <c r="C285" s="38"/>
       <c r="D285" s="38"/>
@@ -30337,7 +30439,7 @@
       <c r="AD285" s="38"/>
       <c r="AE285" s="38"/>
     </row>
-    <row r="286" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B286" s="38"/>
       <c r="C286" s="38"/>
       <c r="D286" s="38"/>
@@ -30369,7 +30471,7 @@
       <c r="AD286" s="38"/>
       <c r="AE286" s="38"/>
     </row>
-    <row r="287" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B287" s="38"/>
       <c r="C287" s="38"/>
       <c r="D287" s="38"/>
@@ -30401,7 +30503,7 @@
       <c r="AD287" s="38"/>
       <c r="AE287" s="38"/>
     </row>
-    <row r="288" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B288" s="38"/>
       <c r="C288" s="38"/>
       <c r="D288" s="38"/>
@@ -30433,7 +30535,7 @@
       <c r="AD288" s="38"/>
       <c r="AE288" s="38"/>
     </row>
-    <row r="289" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B289" s="38"/>
       <c r="C289" s="38"/>
       <c r="D289" s="38"/>
@@ -30465,7 +30567,7 @@
       <c r="AD289" s="38"/>
       <c r="AE289" s="38"/>
     </row>
-    <row r="290" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B290" s="38"/>
       <c r="C290" s="38"/>
       <c r="D290" s="38"/>
@@ -30497,7 +30599,7 @@
       <c r="AD290" s="38"/>
       <c r="AE290" s="38"/>
     </row>
-    <row r="293" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B293" s="38"/>
       <c r="C293" s="38"/>
       <c r="D293" s="38"/>
@@ -30529,7 +30631,7 @@
       <c r="AD293" s="38"/>
       <c r="AE293" s="38"/>
     </row>
-    <row r="294" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B294" s="38"/>
       <c r="C294" s="38"/>
       <c r="D294" s="38"/>
@@ -30561,7 +30663,7 @@
       <c r="AD294" s="38"/>
       <c r="AE294" s="38"/>
     </row>
-    <row r="295" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B295" s="38"/>
       <c r="C295" s="38"/>
       <c r="D295" s="38"/>
@@ -30593,7 +30695,7 @@
       <c r="AD295" s="38"/>
       <c r="AE295" s="38"/>
     </row>
-    <row r="296" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B296" s="38"/>
       <c r="C296" s="38"/>
       <c r="D296" s="38"/>
@@ -30625,7 +30727,7 @@
       <c r="AD296" s="38"/>
       <c r="AE296" s="38"/>
     </row>
-    <row r="297" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B297" s="38"/>
       <c r="C297" s="38"/>
       <c r="D297" s="38"/>
@@ -30657,7 +30759,7 @@
       <c r="AD297" s="38"/>
       <c r="AE297" s="38"/>
     </row>
-    <row r="298" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B298" s="38"/>
       <c r="C298" s="38"/>
       <c r="D298" s="38"/>
@@ -30689,7 +30791,7 @@
       <c r="AD298" s="38"/>
       <c r="AE298" s="38"/>
     </row>
-    <row r="299" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B299" s="38"/>
       <c r="C299" s="38"/>
       <c r="D299" s="38"/>
@@ -30721,7 +30823,7 @@
       <c r="AD299" s="38"/>
       <c r="AE299" s="38"/>
     </row>
-    <row r="300" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B300" s="38"/>
       <c r="C300" s="38"/>
       <c r="D300" s="38"/>
@@ -30754,6 +30856,7 @@
       <c r="AE300" s="38"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -30764,14 +30867,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.85546875" customWidth="1"/>
+    <col min="1" max="1" width="44.875" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>170</v>
       </c>
@@ -30866,7 +30969,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -30961,7 +31064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -31056,7 +31159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -31151,7 +31254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -31246,7 +31349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -31341,7 +31444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -31436,7 +31539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -31531,7 +31634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -31626,102 +31729,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!B1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!B282</f>
         <v>0</v>
       </c>
       <c r="C10">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!C1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!C282</f>
         <v>0</v>
       </c>
       <c r="D10">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!D1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!D282</f>
         <v>0</v>
       </c>
       <c r="E10">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!E1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!E282</f>
         <v>0</v>
       </c>
       <c r="F10">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!F1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!F282</f>
         <v>0</v>
       </c>
       <c r="G10">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!G1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!G282</f>
         <v>0</v>
       </c>
       <c r="H10">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!H1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!H282</f>
         <v>0</v>
       </c>
       <c r="I10">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!I1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!I282</f>
         <v>0</v>
       </c>
       <c r="J10">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!J1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!J282</f>
         <v>0</v>
       </c>
       <c r="K10">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!K1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!K282</f>
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!L1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!L282</f>
+        <v>7.2509451221701132E-2</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!M1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!M282</f>
+        <v>0.14632284781067265</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!N1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!N282</f>
+        <v>0.22430075484895337</v>
       </c>
       <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!O1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!O282</f>
+        <v>0.30144254993781433</v>
+      </c>
+      <c r="P10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!P282</f>
+        <v>0.38143496250418402</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!Q282</f>
+        <v>0.38680033207566089</v>
+      </c>
+      <c r="R10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!R282</f>
+        <v>0.39213297034452449</v>
+      </c>
+      <c r="S10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!S282</f>
+        <v>0.39776118757096762</v>
+      </c>
+      <c r="T10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!T282</f>
+        <v>0.40116769069246927</v>
+      </c>
+      <c r="U10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!U282</f>
+        <v>0.40423294863096948</v>
+      </c>
+      <c r="V10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!V282</f>
+        <v>0.4066410742212464</v>
+      </c>
+      <c r="W10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!W282</f>
+        <v>0.40695687685312182</v>
+      </c>
+      <c r="X10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!X282</f>
+        <v>0.41190037995797696</v>
+      </c>
+      <c r="Y10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!Y282</f>
+        <v>0.41843989759215883</v>
+      </c>
+      <c r="Z10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!Z282</f>
+        <v>0.42562747195359713</v>
+      </c>
+      <c r="AA10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AA282</f>
+        <v>0.43504830369339176</v>
+      </c>
+      <c r="AB10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AB282</f>
+        <v>0.43798494442214675</v>
+      </c>
+      <c r="AC10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AC282</f>
+        <v>0.43361109650911933</v>
+      </c>
+      <c r="AD10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AD282</f>
+        <v>0.43598395826140429</v>
+      </c>
+      <c r="AE10" s="38">
+        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AE282</f>
+        <v>0.44217981007790547</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -31816,7 +31949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -31911,7 +32044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -32006,7 +32139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -32101,7 +32234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -32196,7 +32329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -32291,7 +32424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -32386,7 +32519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -32481,7 +32614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -32576,7 +32709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -32671,7 +32804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -32766,7 +32899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -32861,7 +32994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -32956,7 +33089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -33051,7 +33184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -33146,7 +33279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -33242,6 +33375,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -33253,14 +33387,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.85546875" customWidth="1"/>
+    <col min="1" max="1" width="44.875" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>170</v>
       </c>
@@ -33355,7 +33489,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -33450,7 +33584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -33545,102 +33679,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B6</f>
+        <v>0.21472747612426446</v>
+      </c>
+      <c r="C4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C6</f>
+        <v>0.21508482860112188</v>
+      </c>
+      <c r="D4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D6</f>
+        <v>0.22069008404254345</v>
+      </c>
+      <c r="E4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E6</f>
+        <v>0.21979339457147218</v>
+      </c>
+      <c r="F4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F6</f>
+        <v>0.22908344617435641</v>
+      </c>
+      <c r="G4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G6</f>
+        <v>0.23331697478668498</v>
+      </c>
+      <c r="H4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H6</f>
+        <v>0.23408573257966597</v>
+      </c>
+      <c r="I4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I6</f>
+        <v>0.23374166379457553</v>
+      </c>
+      <c r="J4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J6</f>
+        <v>0.23266612915727847</v>
+      </c>
+      <c r="K4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K6</f>
+        <v>0.23394199621627729</v>
+      </c>
+      <c r="L4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L6</f>
+        <v>0.23540239523069187</v>
+      </c>
+      <c r="M4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M6</f>
+        <v>0.23791103389500834</v>
+      </c>
+      <c r="N4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N6</f>
+        <v>0.23966354205254939</v>
+      </c>
+      <c r="O4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O6</f>
+        <v>0.23899126345235353</v>
+      </c>
+      <c r="P4" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P6</f>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="Q4" s="38">
+        <f>P4</f>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="R4" s="38">
+        <f t="shared" ref="R4:AE4" si="0">Q4</f>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="S4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="T4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="U4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="V4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="W4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="X4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="Y4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="Z4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="AA4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="AB4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="AC4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="AD4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+      <c r="AE4" s="38">
+        <f t="shared" si="0"/>
+        <v>0.23823611380356544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -33735,7 +33899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -33830,7 +33994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -33925,7 +34089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -34020,7 +34184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -34115,102 +34279,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B12</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C12</f>
+        <v>1.7035952458279224E-2</v>
+      </c>
+      <c r="D10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D12</f>
+        <v>7.379540142338728E-2</v>
+      </c>
+      <c r="E10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E12</f>
+        <v>0.12978043460134511</v>
+      </c>
+      <c r="F10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F12</f>
+        <v>0.18340143676845078</v>
+      </c>
+      <c r="G10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G12</f>
+        <v>0.23726323944903455</v>
+      </c>
+      <c r="H10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H12</f>
+        <v>0.29179797708222832</v>
+      </c>
+      <c r="I10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I12</f>
+        <v>0.3465888690181968</v>
+      </c>
+      <c r="J10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J12</f>
+        <v>0.40293807245549862</v>
+      </c>
+      <c r="K10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K12</f>
+        <v>0.46127828033038998</v>
+      </c>
+      <c r="L10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L12</f>
+        <v>0.46428938925855379</v>
+      </c>
+      <c r="M10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M12</f>
+        <v>0.46892634931043969</v>
+      </c>
+      <c r="N10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N12</f>
+        <v>0.47908528156881697</v>
+      </c>
+      <c r="O10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O12</f>
+        <v>0.48916293796855054</v>
+      </c>
+      <c r="P10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P12</f>
+        <v>0.49657659767289786</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Q12</f>
+        <v>0.50296540850885785</v>
+      </c>
+      <c r="R10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!R12</f>
+        <v>0.51456524577321661</v>
+      </c>
+      <c r="S10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!S12</f>
+        <v>0.52416240494873922</v>
+      </c>
+      <c r="T10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!T12</f>
+        <v>0.5337411036527685</v>
+      </c>
+      <c r="U10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!U12</f>
+        <v>0.54446206562073074</v>
+      </c>
+      <c r="V10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!V12</f>
+        <v>0.55091923685396671</v>
+      </c>
+      <c r="W10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!W12</f>
+        <v>0.55490684703794002</v>
+      </c>
+      <c r="X10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!X12</f>
+        <v>0.5637005765733456</v>
+      </c>
+      <c r="Y10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Y12</f>
+        <v>0.56928750459812449</v>
+      </c>
+      <c r="Z10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Z12</f>
+        <v>0.57880294177833458</v>
+      </c>
+      <c r="AA10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AA12</f>
+        <v>0.58666244942241519</v>
+      </c>
+      <c r="AB10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AB12</f>
+        <v>0.60164854466283457</v>
+      </c>
+      <c r="AC10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AC12</f>
+        <v>0.61282270980178088</v>
+      </c>
+      <c r="AD10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AD12</f>
+        <v>0.61033926350690149</v>
+      </c>
+      <c r="AE10" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AE12</f>
+        <v>0.61297940852101807</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -34305,7 +34499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -34400,7 +34594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -34495,197 +34689,257 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B16</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C16</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D16</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F16</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H16</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I16</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J16</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K16</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L16</f>
+        <v>0.12584183275816249</v>
+      </c>
+      <c r="M14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M16</f>
+        <v>0.24902718409452954</v>
+      </c>
+      <c r="N14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N16</f>
+        <v>0.37063322693604867</v>
+      </c>
+      <c r="O14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O16</f>
+        <v>0.49229651422155546</v>
+      </c>
+      <c r="P14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P16</f>
+        <v>0.61089208806394202</v>
+      </c>
+      <c r="Q14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Q16</f>
+        <v>0.60113262212048835</v>
+      </c>
+      <c r="R14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!R16</f>
+        <v>0.59361131092300634</v>
+      </c>
+      <c r="S14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!S16</f>
+        <v>0.58777591828937059</v>
+      </c>
+      <c r="T14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!T16</f>
+        <v>0.58158880336000873</v>
+      </c>
+      <c r="U14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!U16</f>
+        <v>0.57705234918255754</v>
+      </c>
+      <c r="V14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!V16</f>
+        <v>0.57101307812884161</v>
+      </c>
+      <c r="W14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!W16</f>
+        <v>0.56378506448164112</v>
+      </c>
+      <c r="X14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!X16</f>
+        <v>0.55816163289218235</v>
+      </c>
+      <c r="Y14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Y16</f>
+        <v>0.55553315123035074</v>
+      </c>
+      <c r="Z14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Z16</f>
+        <v>0.54979518443341302</v>
+      </c>
+      <c r="AA14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AA16</f>
+        <v>0.54349694548834093</v>
+      </c>
+      <c r="AB14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AB16</f>
+        <v>0.53853472784908896</v>
+      </c>
+      <c r="AC14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AC16</f>
+        <v>0.53346663031249886</v>
+      </c>
+      <c r="AD14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AD16</f>
+        <v>0.52939041470186365</v>
+      </c>
+      <c r="AE14" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AE16</f>
+        <v>0.52524957511634962</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B17</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D17</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E17</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F17</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H17</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I17</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J17</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K17</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L17</f>
+        <v>5.9126788165476771E-2</v>
+      </c>
+      <c r="M15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M17</f>
+        <v>0.11856907216886765</v>
+      </c>
+      <c r="N15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N17</f>
+        <v>0.17576472359261788</v>
+      </c>
+      <c r="O15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O17</f>
+        <v>0.23485961304457414</v>
+      </c>
+      <c r="P15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P17</f>
+        <v>0.29224072486387437</v>
+      </c>
+      <c r="Q15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Q17</f>
+        <v>0.29029708108805763</v>
+      </c>
+      <c r="R15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!R17</f>
+        <v>0.28995271918878357</v>
+      </c>
+      <c r="S15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!S17</f>
+        <v>0.28715947165900441</v>
+      </c>
+      <c r="T15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!T17</f>
+        <v>0.28468453561162887</v>
+      </c>
+      <c r="U15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!U17</f>
+        <v>0.28501649052722078</v>
+      </c>
+      <c r="V15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!V17</f>
+        <v>0.28310185577501101</v>
+      </c>
+      <c r="W15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!W17</f>
+        <v>0.27877525350837651</v>
+      </c>
+      <c r="X15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!X17</f>
+        <v>0.27669248616271735</v>
+      </c>
+      <c r="Y15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Y17</f>
+        <v>0.27625468159600419</v>
+      </c>
+      <c r="Z15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Z17</f>
+        <v>0.27769841203833734</v>
+      </c>
+      <c r="AA15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AA17</f>
+        <v>0.27960437231313717</v>
+      </c>
+      <c r="AB15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AB17</f>
+        <v>0.28037410217497655</v>
+      </c>
+      <c r="AC15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AC17</f>
+        <v>0.28011705509528367</v>
+      </c>
+      <c r="AD15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AD17</f>
+        <v>0.27826746616136672</v>
+      </c>
+      <c r="AE15" s="38">
+        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AE17</f>
+        <v>0.27732033387354721</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -34780,7 +35034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -34875,7 +35129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -34970,7 +35224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -35065,7 +35319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -35160,7 +35414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -35255,7 +35509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -35350,7 +35604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -35445,7 +35699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -35540,7 +35794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -35635,7 +35889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -35731,27 +35985,13 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -35895,24 +36135,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDA22ACB-0B36-444A-9EDB-569170CC84C9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C87C9ED-B778-4193-A9C3-B7949AEFF542}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25E8880E-AF2E-48F4-A23A-B08EB814F290}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35928,4 +36166,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDA22ACB-0B36-444A-9EDB-569170CC84C9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C87C9ED-B778-4193-A9C3-B7949AEFF542}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/ccs/BFoCPAbI/BAU Fraction of CCS Potential Achieved by Industry.xlsx
+++ b/InputData/ccs/BFoCPAbI/BAU Fraction of CCS Potential Achieved by Industry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\administer\Dropbox\kjh\2025\02. EPS\EI\251020_메일회신\회신용 파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\ccs\BFoCPAbI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2460D45A-65CA-40F5-91ED-5B2A573F9111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B63D7B4-F756-4D4F-AE86-780EFE8E5A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29520" yWindow="225" windowWidth="24810" windowHeight="14865" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1408,7 +1408,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -1417,39 +1417,28 @@
     </r>
   </si>
   <si>
+    <t>South Korea Context</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.plan15.org/press/?bmode=view&amp;idx=161107222&amp;utm_source=chatgpt.com</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Therefore, to enhance the realism of the simulation, we will </t>
+      <t xml:space="preserve">Therefore, to enhance the realism of the simulation, we will zero out </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>use the latest CCS-related data from the United States</t>
+      <t xml:space="preserve">CCS potential achieved </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> instead of Korean data to set the initial modeling parameters.</t>
-    </r>
-  </si>
-  <si>
-    <t>South Korea Context</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.plan15.org/press/?bmode=view&amp;idx=161107222&amp;utm_source=chatgpt.com</t>
   </si>
 </sst>
 </file>
@@ -1457,14 +1446,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1472,7 +1461,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1480,14 +1469,14 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1495,14 +1484,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1511,14 +1500,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1666,7 +1655,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1716,7 +1705,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1726,9 +1715,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="백분율" xfId="1" builtinId="5"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2129,20 +2118,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="103.375" customWidth="1"/>
-    <col min="3" max="3" width="17.125" customWidth="1"/>
-    <col min="4" max="4" width="22.125" customWidth="1"/>
-    <col min="5" max="5" width="18.375" customWidth="1"/>
+    <col min="2" max="2" width="103.36328125" customWidth="1"/>
+    <col min="3" max="3" width="17.08984375" customWidth="1"/>
+    <col min="4" max="4" width="22.08984375" customWidth="1"/>
+    <col min="5" max="5" width="18.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -2150,75 +2139,75 @@
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="B5" s="8">
         <v>2023</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="B7" s="9" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="B9" s="9"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="B10" s="10" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="B12" s="8">
         <v>2022</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="B14" s="37" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="B15" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="B17" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="B18" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="B19" s="8">
         <v>2019</v>
       </c>
@@ -2226,88 +2215,88 @@
       <c r="D19" s="3"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="B20" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="B21" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="B22" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="B23" s="8"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>34</v>
       </c>
       <c r="B30" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1">
       <c r="A37" s="40" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
       <c r="A38" s="39" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1">
       <c r="A39" s="39" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -2324,20 +2313,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9816DDC5-B47D-412D-83A1-985DCFECCE82}">
   <dimension ref="A1:I48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="47.75" customWidth="1"/>
-    <col min="2" max="2" width="25.75" customWidth="1"/>
-    <col min="3" max="3" width="18.875" customWidth="1"/>
-    <col min="4" max="4" width="27.875" customWidth="1"/>
-    <col min="5" max="5" width="12.125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="30.125" customWidth="1"/>
-    <col min="7" max="7" width="26.25" customWidth="1"/>
-    <col min="8" max="8" width="37.25" customWidth="1"/>
-    <col min="9" max="9" width="31.125" customWidth="1"/>
+    <col min="1" max="1" width="47.7265625" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" customWidth="1"/>
+    <col min="3" max="3" width="18.90625" customWidth="1"/>
+    <col min="4" max="4" width="27.90625" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="30.08984375" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" customWidth="1"/>
+    <col min="8" max="8" width="37.26953125" customWidth="1"/>
+    <col min="9" max="9" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="23" t="s">
         <v>115</v>
       </c>
@@ -2350,7 +2339,7 @@
       <c r="H1" s="20"/>
       <c r="I1" s="20"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>114</v>
       </c>
@@ -2379,7 +2368,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>106</v>
       </c>
@@ -2402,7 +2391,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -2422,7 +2411,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -2445,7 +2434,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>103</v>
       </c>
@@ -2468,7 +2457,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -2494,7 +2483,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>99</v>
       </c>
@@ -2517,7 +2506,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>98</v>
       </c>
@@ -2537,7 +2526,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>97</v>
       </c>
@@ -2560,7 +2549,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>95</v>
       </c>
@@ -2580,7 +2569,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="87">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -2606,7 +2595,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -2626,7 +2615,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -2646,7 +2635,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -2672,7 +2661,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>85</v>
       </c>
@@ -2695,7 +2684,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -2721,7 +2710,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -2747,7 +2736,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -2770,7 +2759,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>77</v>
       </c>
@@ -2793,7 +2782,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>75</v>
       </c>
@@ -2819,7 +2808,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -2839,7 +2828,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -2865,7 +2854,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -2888,7 +2877,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -2908,7 +2897,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2931,7 +2920,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -2954,7 +2943,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -2977,7 +2966,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -2997,7 +2986,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>53</v>
       </c>
@@ -3023,13 +3012,13 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B34" s="15"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -3038,7 +3027,7 @@
         <v>28.360000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -3047,13 +3036,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B39" s="13"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -3066,7 +3055,7 @@
         <v>0.6921272158498436</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -3079,7 +3068,7 @@
         <v>4.6923879040667367E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -3092,7 +3081,7 @@
         <v>7.8206465067778938E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -3105,7 +3094,7 @@
         <v>5.7351407716371226E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -3118,7 +3107,7 @@
         <v>3.6496350364963501E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -3131,7 +3120,7 @@
         <v>2.0855057351407719E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -3144,7 +3133,7 @@
         <v>3.6235662148070912E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>36</v>
       </c>
@@ -3157,7 +3146,7 @@
         <v>5.7351407716371219E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>35</v>
       </c>
@@ -3188,30 +3177,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED05A5AB-C865-4DF5-BD35-041C1CC241DD}">
   <dimension ref="A1:H48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.125" customWidth="1"/>
-    <col min="2" max="2" width="18.875" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="20.25" customWidth="1"/>
-    <col min="5" max="5" width="19.625" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
-    <col min="7" max="7" width="17.75" customWidth="1"/>
+    <col min="1" max="1" width="24.08984375" customWidth="1"/>
+    <col min="2" max="2" width="18.90625" customWidth="1"/>
+    <col min="3" max="3" width="10.36328125" customWidth="1"/>
+    <col min="4" max="4" width="20.26953125" customWidth="1"/>
+    <col min="5" max="5" width="19.6328125" customWidth="1"/>
+    <col min="6" max="6" width="14.6328125" customWidth="1"/>
+    <col min="7" max="7" width="17.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="6" t="s">
         <v>151</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2000</v>
       </c>
@@ -3219,7 +3208,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>2015</v>
       </c>
@@ -3227,7 +3216,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>2020</v>
       </c>
@@ -3238,7 +3227,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -3249,19 +3238,19 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
         <v>149</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="36" t="s">
         <v>147</v>
       </c>
@@ -3272,7 +3261,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="34">
         <v>0.56999999999999995</v>
       </c>
@@ -3284,7 +3273,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="34">
         <v>0.34</v>
       </c>
@@ -3296,7 +3285,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="34">
         <v>0.03</v>
       </c>
@@ -3308,7 +3297,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="34">
         <v>0.03</v>
       </c>
@@ -3320,7 +3309,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="34">
         <v>0.02</v>
       </c>
@@ -3332,7 +3321,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="34">
         <v>0.04</v>
       </c>
@@ -3344,49 +3333,49 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B18" s="5"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" s="34">
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" s="34" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" s="6" t="s">
         <v>136</v>
       </c>
       <c r="B24" s="5"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>70</v>
       </c>
@@ -3394,12 +3383,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>80</v>
       </c>
@@ -3407,12 +3396,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" s="3">
         <f>B5*B12</f>
         <v>82.524271844660205</v>
@@ -3421,8 +3410,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="15" thickBot="1"/>
+    <row r="33" spans="1:8">
       <c r="A33" s="33" t="s">
         <v>128</v>
       </c>
@@ -3433,7 +3422,7 @@
       <c r="F33" s="32"/>
       <c r="G33" s="31"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34" s="28"/>
       <c r="B34" s="29" t="s">
         <v>127</v>
@@ -3457,7 +3446,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35" s="28" t="s">
         <v>121</v>
       </c>
@@ -3488,7 +3477,7 @@
         <v>167.47572815533979</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36" s="28" t="s">
         <v>120</v>
       </c>
@@ -3517,7 +3506,7 @@
         <v>33.486929491831802</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="15" thickBot="1">
       <c r="A37" s="26" t="s">
         <v>119</v>
       </c>
@@ -3545,37 +3534,37 @@
         <v>57.76699029126214</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="C38" s="2"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42">
         <f>'Operational Capacity'!B35</f>
         <v>28.360000000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8">
       <c r="A45" s="12">
         <f>C36/A42</f>
         <v>0.87296479384337322</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8">
       <c r="A48" s="3">
         <f>A45*'Operational Capacity'!B36</f>
         <v>8.7296479384337324</v>
@@ -3590,12 +3579,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{000817FC-5CAD-42B5-92F8-1A675198574D}">
   <dimension ref="A25:H54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="48.25" customWidth="1"/>
+    <col min="1" max="1" width="48.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25" s="6" t="s">
         <v>171</v>
       </c>
@@ -3607,7 +3596,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="B26">
         <v>2022</v>
       </c>
@@ -3618,17 +3607,17 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -3642,32 +3631,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>175</v>
       </c>
@@ -3684,7 +3673,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>176</v>
       </c>
@@ -3701,7 +3690,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -3709,17 +3698,17 @@
         <v>177</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -3733,7 +3722,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -3747,62 +3736,62 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>122</v>
       </c>
@@ -3829,17 +3818,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D869D793-4D45-441A-BEF3-5973BA28AC13}">
   <dimension ref="A1:AE300"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="80.125" customWidth="1"/>
+    <col min="1" max="1" width="80.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>172</v>
       </c>
@@ -3934,7 +3923,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>179</v>
       </c>
@@ -4029,7 +4018,7 @@
         <v>9716000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>180</v>
       </c>
@@ -4124,7 +4113,7 @@
         <v>665338000000</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>181</v>
       </c>
@@ -4219,7 +4208,7 @@
         <v>69366600000000</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>182</v>
       </c>
@@ -4314,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>183</v>
       </c>
@@ -4409,7 +4398,7 @@
         <v>6699000000000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
         <v>184</v>
       </c>
@@ -4504,7 +4493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
         <v>185</v>
       </c>
@@ -4599,7 +4588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
         <v>186</v>
       </c>
@@ -4694,7 +4683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
         <v>187</v>
       </c>
@@ -4789,7 +4778,7 @@
         <v>75479100000000</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
         <v>188</v>
       </c>
@@ -4884,7 +4873,7 @@
         <v>160400000000000</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
         <v>189</v>
       </c>
@@ -4979,7 +4968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
         <v>190</v>
       </c>
@@ -5074,7 +5063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
         <v>191</v>
       </c>
@@ -5169,7 +5158,7 @@
         <v>83100000000000</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31">
       <c r="A17" t="s">
         <v>192</v>
       </c>
@@ -5264,7 +5253,7 @@
         <v>44070000000000</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31">
       <c r="A18" t="s">
         <v>193</v>
       </c>
@@ -5359,7 +5348,7 @@
         <v>5642000000000</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31">
       <c r="A19" t="s">
         <v>194</v>
       </c>
@@ -5454,7 +5443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31">
       <c r="A20" t="s">
         <v>195</v>
       </c>
@@ -5549,7 +5538,7 @@
         <v>546600000000</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31">
       <c r="A21" t="s">
         <v>196</v>
       </c>
@@ -5644,7 +5633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31">
       <c r="A22" t="s">
         <v>197</v>
       </c>
@@ -5739,7 +5728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31">
       <c r="A23" t="s">
         <v>198</v>
       </c>
@@ -5834,7 +5823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31">
       <c r="A24" t="s">
         <v>199</v>
       </c>
@@ -5929,7 +5918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31">
       <c r="A25" t="s">
         <v>200</v>
       </c>
@@ -6024,7 +6013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31">
       <c r="A26" t="s">
         <v>201</v>
       </c>
@@ -6119,7 +6108,7 @@
         <v>1400230000000</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31">
       <c r="A27" t="s">
         <v>202</v>
       </c>
@@ -6214,7 +6203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31">
       <c r="A28" t="s">
         <v>203</v>
       </c>
@@ -6309,7 +6298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31">
       <c r="B29" s="38"/>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -6341,7 +6330,7 @@
       <c r="AD29" s="38"/>
       <c r="AE29" s="38"/>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31">
       <c r="A30" t="s">
         <v>172</v>
       </c>
@@ -6436,7 +6425,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31">
       <c r="A31" t="s">
         <v>204</v>
       </c>
@@ -6531,7 +6520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31">
       <c r="A32" t="s">
         <v>205</v>
       </c>
@@ -6626,7 +6615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:31">
       <c r="A33" t="s">
         <v>206</v>
       </c>
@@ -6721,7 +6710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:31">
       <c r="A34" t="s">
         <v>207</v>
       </c>
@@ -6816,7 +6805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:31">
       <c r="A35" t="s">
         <v>208</v>
       </c>
@@ -6911,7 +6900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:31">
       <c r="A36" t="s">
         <v>209</v>
       </c>
@@ -7006,7 +6995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:31">
       <c r="A37" t="s">
         <v>210</v>
       </c>
@@ -7101,7 +7090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31">
       <c r="A38" t="s">
         <v>211</v>
       </c>
@@ -7196,7 +7185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31">
       <c r="A39" t="s">
         <v>212</v>
       </c>
@@ -7291,7 +7280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:31">
       <c r="A40" t="s">
         <v>213</v>
       </c>
@@ -7386,7 +7375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:31">
       <c r="A41" t="s">
         <v>214</v>
       </c>
@@ -7481,7 +7470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31">
       <c r="A42" t="s">
         <v>215</v>
       </c>
@@ -7576,7 +7565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:31">
       <c r="A43" t="s">
         <v>216</v>
       </c>
@@ -7671,7 +7660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:31">
       <c r="A44" t="s">
         <v>217</v>
       </c>
@@ -7766,7 +7755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:31">
       <c r="A45" t="s">
         <v>218</v>
       </c>
@@ -7861,7 +7850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:31">
       <c r="A46" t="s">
         <v>219</v>
       </c>
@@ -7956,7 +7945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:31">
       <c r="A47" t="s">
         <v>220</v>
       </c>
@@ -8051,7 +8040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:31">
       <c r="A48" t="s">
         <v>221</v>
       </c>
@@ -8146,7 +8135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:31">
       <c r="A49" t="s">
         <v>222</v>
       </c>
@@ -8241,7 +8230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:31">
       <c r="A50" t="s">
         <v>223</v>
       </c>
@@ -8336,7 +8325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:31">
       <c r="A51" t="s">
         <v>224</v>
       </c>
@@ -8431,7 +8420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:31">
       <c r="A52" t="s">
         <v>225</v>
       </c>
@@ -8526,7 +8515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:31">
       <c r="A53" t="s">
         <v>226</v>
       </c>
@@ -8621,7 +8610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:31">
       <c r="A54" t="s">
         <v>227</v>
       </c>
@@ -8716,7 +8705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:31">
       <c r="A55" t="s">
         <v>228</v>
       </c>
@@ -8811,7 +8800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:31">
       <c r="A56" t="s">
         <v>229</v>
       </c>
@@ -8906,7 +8895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:31">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -9001,7 +8990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:31">
       <c r="A58" t="s">
         <v>231</v>
       </c>
@@ -9096,7 +9085,7 @@
         <v>11727400000</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:31">
       <c r="A59" t="s">
         <v>232</v>
       </c>
@@ -9191,7 +9180,7 @@
         <v>867461000000</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:31">
       <c r="A60" t="s">
         <v>233</v>
       </c>
@@ -9286,7 +9275,7 @@
         <v>13310600000000</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:31">
       <c r="A61" t="s">
         <v>234</v>
       </c>
@@ -9381,7 +9370,7 @@
         <v>479409000000</v>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:31">
       <c r="A62" t="s">
         <v>235</v>
       </c>
@@ -9476,7 +9465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:31">
       <c r="A63" t="s">
         <v>236</v>
       </c>
@@ -9571,7 +9560,7 @@
         <v>1238280000000</v>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:31">
       <c r="A64" t="s">
         <v>237</v>
       </c>
@@ -9666,7 +9655,7 @@
         <v>1923620000000</v>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:31">
       <c r="A65" t="s">
         <v>238</v>
       </c>
@@ -9761,7 +9750,7 @@
         <v>5779600000000</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:31">
       <c r="A66" t="s">
         <v>239</v>
       </c>
@@ -9856,7 +9845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:31">
       <c r="A67" t="s">
         <v>240</v>
       </c>
@@ -9951,7 +9940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:31">
       <c r="A68" t="s">
         <v>241</v>
       </c>
@@ -10046,7 +10035,7 @@
         <v>4095420000000</v>
       </c>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:31">
       <c r="A69" t="s">
         <v>242</v>
       </c>
@@ -10141,7 +10130,7 @@
         <v>5339520000000</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:31">
       <c r="A70" t="s">
         <v>243</v>
       </c>
@@ -10236,7 +10225,7 @@
         <v>410773000000</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:31">
       <c r="A71" t="s">
         <v>244</v>
       </c>
@@ -10331,7 +10320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:31">
       <c r="A72" t="s">
         <v>245</v>
       </c>
@@ -10426,7 +10415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:31">
       <c r="A73" t="s">
         <v>246</v>
       </c>
@@ -10521,7 +10510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:31">
       <c r="A74" t="s">
         <v>247</v>
       </c>
@@ -10616,7 +10605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:31">
       <c r="A75" t="s">
         <v>248</v>
       </c>
@@ -10711,7 +10700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:31">
       <c r="A76" t="s">
         <v>249</v>
       </c>
@@ -10806,7 +10795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:31">
       <c r="A77" t="s">
         <v>250</v>
       </c>
@@ -10901,7 +10890,7 @@
         <v>1496730000000</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:31">
       <c r="A78" t="s">
         <v>251</v>
       </c>
@@ -10996,7 +10985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:31">
       <c r="A79" t="s">
         <v>252</v>
       </c>
@@ -11091,7 +11080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:31">
       <c r="A80" t="s">
         <v>253</v>
       </c>
@@ -11186,7 +11175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:31">
       <c r="A81" t="s">
         <v>254</v>
       </c>
@@ -11281,7 +11270,7 @@
         <v>6462710000000</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:31">
       <c r="A82" t="s">
         <v>255</v>
       </c>
@@ -11376,7 +11365,7 @@
         <v>109816000000</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:31">
       <c r="A83" t="s">
         <v>256</v>
       </c>
@@ -11471,7 +11460,7 @@
         <v>155700000000000</v>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:31">
       <c r="A84" t="s">
         <v>257</v>
       </c>
@@ -11566,7 +11555,7 @@
         <v>9168770000000</v>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:31">
       <c r="A85" t="s">
         <v>258</v>
       </c>
@@ -11661,7 +11650,7 @@
         <v>46034900000000</v>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:31">
       <c r="A86" t="s">
         <v>259</v>
       </c>
@@ -11756,7 +11745,7 @@
         <v>6696170000000</v>
       </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:31">
       <c r="A87" t="s">
         <v>260</v>
       </c>
@@ -11851,7 +11840,7 @@
         <v>2512390000000</v>
       </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:31">
       <c r="A88" t="s">
         <v>261</v>
       </c>
@@ -11946,7 +11935,7 @@
         <v>22099500000000</v>
       </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:31">
       <c r="A89" t="s">
         <v>262</v>
       </c>
@@ -12041,7 +12030,7 @@
         <v>21011700000000</v>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:31">
       <c r="A90" t="s">
         <v>263</v>
       </c>
@@ -12136,7 +12125,7 @@
         <v>146795000000000</v>
       </c>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:31">
       <c r="A91" t="s">
         <v>264</v>
       </c>
@@ -12231,7 +12220,7 @@
         <v>5682730000000</v>
       </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:31">
       <c r="A92" t="s">
         <v>265</v>
       </c>
@@ -12326,7 +12315,7 @@
         <v>4059090000000</v>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:31">
       <c r="A93" t="s">
         <v>266</v>
       </c>
@@ -12421,7 +12410,7 @@
         <v>10214100000000</v>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:31">
       <c r="A94" t="s">
         <v>267</v>
       </c>
@@ -12516,7 +12505,7 @@
         <v>18213300000000</v>
       </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:31">
       <c r="A95" t="s">
         <v>268</v>
       </c>
@@ -12611,7 +12600,7 @@
         <v>11625400000000</v>
       </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:31">
       <c r="A96" t="s">
         <v>269</v>
       </c>
@@ -12706,7 +12695,7 @@
         <v>7104730000000</v>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:31">
       <c r="A97" t="s">
         <v>270</v>
       </c>
@@ -12801,7 +12790,7 @@
         <v>1530250000000</v>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:31">
       <c r="A98" t="s">
         <v>271</v>
       </c>
@@ -12896,7 +12885,7 @@
         <v>2385050000000</v>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:31">
       <c r="A99" t="s">
         <v>272</v>
       </c>
@@ -12991,7 +12980,7 @@
         <v>3633550000000</v>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:31">
       <c r="A100" t="s">
         <v>273</v>
       </c>
@@ -13086,7 +13075,7 @@
         <v>6717400000000</v>
       </c>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:31">
       <c r="A101" t="s">
         <v>274</v>
       </c>
@@ -13181,7 +13170,7 @@
         <v>3802810000000</v>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:31">
       <c r="A102" t="s">
         <v>275</v>
       </c>
@@ -13276,7 +13265,7 @@
         <v>20910900000000</v>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:31">
       <c r="A103" t="s">
         <v>276</v>
       </c>
@@ -13371,7 +13360,7 @@
         <v>41048000000000</v>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:31">
       <c r="A104" t="s">
         <v>277</v>
       </c>
@@ -13466,7 +13455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:31">
       <c r="A105" t="s">
         <v>278</v>
       </c>
@@ -13561,7 +13550,7 @@
         <v>10394500000000</v>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:31">
       <c r="A106" t="s">
         <v>279</v>
       </c>
@@ -13656,7 +13645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:31">
       <c r="A107" t="s">
         <v>280</v>
       </c>
@@ -13751,7 +13740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:31">
       <c r="A108" t="s">
         <v>281</v>
       </c>
@@ -13846,7 +13835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:31">
       <c r="A109" t="s">
         <v>282</v>
       </c>
@@ -13941,7 +13930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:31">
       <c r="A110" t="s">
         <v>283</v>
       </c>
@@ -14036,7 +14025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:31">
       <c r="A111" t="s">
         <v>284</v>
       </c>
@@ -14131,7 +14120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:31">
       <c r="A112" t="s">
         <v>285</v>
       </c>
@@ -14226,7 +14215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:31">
       <c r="A113" t="s">
         <v>286</v>
       </c>
@@ -14321,7 +14310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:31">
       <c r="A114" t="s">
         <v>287</v>
       </c>
@@ -14416,7 +14405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:31">
       <c r="A115" t="s">
         <v>288</v>
       </c>
@@ -14511,7 +14500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:31">
       <c r="A116" t="s">
         <v>289</v>
       </c>
@@ -14606,7 +14595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:31">
       <c r="A117" t="s">
         <v>290</v>
       </c>
@@ -14701,7 +14690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:31">
       <c r="A118" t="s">
         <v>291</v>
       </c>
@@ -14796,7 +14785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:31">
       <c r="A119" t="s">
         <v>292</v>
       </c>
@@ -14891,7 +14880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:31">
       <c r="A120" t="s">
         <v>293</v>
       </c>
@@ -14986,7 +14975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:31">
       <c r="A121" t="s">
         <v>294</v>
       </c>
@@ -15081,7 +15070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:31">
       <c r="A122" t="s">
         <v>295</v>
       </c>
@@ -15176,7 +15165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:31">
       <c r="A123" t="s">
         <v>296</v>
       </c>
@@ -15271,7 +15260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:31">
       <c r="A124" t="s">
         <v>297</v>
       </c>
@@ -15366,7 +15355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:31">
       <c r="A125" t="s">
         <v>298</v>
       </c>
@@ -15461,7 +15450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:31">
       <c r="A126" t="s">
         <v>299</v>
       </c>
@@ -15556,7 +15545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:31">
       <c r="A127" t="s">
         <v>300</v>
       </c>
@@ -15651,7 +15640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:31">
       <c r="A128" t="s">
         <v>301</v>
       </c>
@@ -15746,7 +15735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:31">
       <c r="A129" t="s">
         <v>302</v>
       </c>
@@ -15841,7 +15830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:31">
       <c r="A130" t="s">
         <v>303</v>
       </c>
@@ -15936,7 +15925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:31">
       <c r="A131" t="s">
         <v>304</v>
       </c>
@@ -16031,7 +16020,7 @@
         <v>47012600000000</v>
       </c>
     </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:31">
       <c r="A132" t="s">
         <v>305</v>
       </c>
@@ -16126,7 +16115,7 @@
         <v>560345000000</v>
       </c>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:31">
       <c r="A133" t="s">
         <v>306</v>
       </c>
@@ -16221,7 +16210,7 @@
         <v>9549060000000</v>
       </c>
     </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:31">
       <c r="A134" t="s">
         <v>307</v>
       </c>
@@ -16316,7 +16305,7 @@
         <v>6406920000000</v>
       </c>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:31">
       <c r="A135" t="s">
         <v>308</v>
       </c>
@@ -16411,7 +16400,7 @@
         <v>967266000000</v>
       </c>
     </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:31">
       <c r="A136" t="s">
         <v>309</v>
       </c>
@@ -16506,7 +16495,7 @@
         <v>358391000000</v>
       </c>
     </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:31">
       <c r="A137" t="s">
         <v>310</v>
       </c>
@@ -16601,7 +16590,7 @@
         <v>548392000000</v>
       </c>
     </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:31">
       <c r="A138" t="s">
         <v>311</v>
       </c>
@@ -16696,7 +16685,7 @@
         <v>739519000000</v>
       </c>
     </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:31">
       <c r="A139" t="s">
         <v>312</v>
       </c>
@@ -16791,7 +16780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:31">
       <c r="A140" t="s">
         <v>313</v>
       </c>
@@ -16886,7 +16875,7 @@
         <v>71258000000</v>
       </c>
     </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:31">
       <c r="A141" t="s">
         <v>314</v>
       </c>
@@ -16981,7 +16970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:31">
       <c r="A142" t="s">
         <v>315</v>
       </c>
@@ -17076,7 +17065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:31">
       <c r="A143" t="s">
         <v>316</v>
       </c>
@@ -17171,7 +17160,7 @@
         <v>4134700000000</v>
       </c>
     </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:31">
       <c r="A144" t="s">
         <v>317</v>
       </c>
@@ -17266,7 +17255,7 @@
         <v>202683000000</v>
       </c>
     </row>
-    <row r="145" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:31">
       <c r="A145" t="s">
         <v>318</v>
       </c>
@@ -17361,7 +17350,7 @@
         <v>362743000000</v>
       </c>
     </row>
-    <row r="146" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:31">
       <c r="A146" t="s">
         <v>319</v>
       </c>
@@ -17456,7 +17445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:31">
       <c r="A147" t="s">
         <v>320</v>
       </c>
@@ -17551,7 +17540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:31">
       <c r="A148" t="s">
         <v>321</v>
       </c>
@@ -17646,7 +17635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:31">
       <c r="A149" t="s">
         <v>322</v>
       </c>
@@ -17741,7 +17730,7 @@
         <v>105131000000</v>
       </c>
     </row>
-    <row r="150" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:31">
       <c r="A150" t="s">
         <v>323</v>
       </c>
@@ -17836,7 +17825,7 @@
         <v>174318000000</v>
       </c>
     </row>
-    <row r="151" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:31">
       <c r="A151" t="s">
         <v>324</v>
       </c>
@@ -17931,7 +17920,7 @@
         <v>98602600000</v>
       </c>
     </row>
-    <row r="152" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:31">
       <c r="A152" t="s">
         <v>325</v>
       </c>
@@ -18026,7 +18015,7 @@
         <v>1119600000000</v>
       </c>
     </row>
-    <row r="153" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:31">
       <c r="A153" t="s">
         <v>326</v>
       </c>
@@ -18121,7 +18110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:31">
       <c r="A154" t="s">
         <v>327</v>
       </c>
@@ -18216,7 +18205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:31">
       <c r="A155" t="s">
         <v>328</v>
       </c>
@@ -18311,7 +18300,7 @@
         <v>42095300000000</v>
       </c>
     </row>
-    <row r="156" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:31">
       <c r="A156" t="s">
         <v>329</v>
       </c>
@@ -18406,7 +18395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:31">
       <c r="A157" t="s">
         <v>330</v>
       </c>
@@ -18501,7 +18490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:31">
       <c r="A158" t="s">
         <v>331</v>
       </c>
@@ -18596,7 +18585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:31">
       <c r="A159" t="s">
         <v>332</v>
       </c>
@@ -18691,7 +18680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:31">
       <c r="A160" t="s">
         <v>333</v>
       </c>
@@ -18786,7 +18775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:31">
       <c r="A161" t="s">
         <v>334</v>
       </c>
@@ -18881,7 +18870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:31">
       <c r="A162" t="s">
         <v>335</v>
       </c>
@@ -18976,7 +18965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:31">
       <c r="A163" t="s">
         <v>336</v>
       </c>
@@ -19071,7 +19060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:31">
       <c r="A164" t="s">
         <v>337</v>
       </c>
@@ -19166,7 +19155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:31">
       <c r="A165" t="s">
         <v>338</v>
       </c>
@@ -19261,7 +19250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:31">
       <c r="A166" t="s">
         <v>339</v>
       </c>
@@ -19356,7 +19345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:31">
       <c r="A167" t="s">
         <v>340</v>
       </c>
@@ -19451,7 +19440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:31">
       <c r="A168" t="s">
         <v>341</v>
       </c>
@@ -19546,7 +19535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:31">
       <c r="A169" t="s">
         <v>342</v>
       </c>
@@ -19641,7 +19630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:31">
       <c r="A170" t="s">
         <v>343</v>
       </c>
@@ -19736,7 +19725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:31">
       <c r="A171" t="s">
         <v>344</v>
       </c>
@@ -19831,7 +19820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:31">
       <c r="A172" t="s">
         <v>345</v>
       </c>
@@ -19926,7 +19915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:31">
       <c r="A173" t="s">
         <v>346</v>
       </c>
@@ -20021,7 +20010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:31">
       <c r="A174" t="s">
         <v>347</v>
       </c>
@@ -20116,7 +20105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:31">
       <c r="A175" t="s">
         <v>348</v>
       </c>
@@ -20211,7 +20200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:31">
       <c r="A176" t="s">
         <v>349</v>
       </c>
@@ -20306,7 +20295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:31">
       <c r="A177" t="s">
         <v>350</v>
       </c>
@@ -20401,7 +20390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:31">
       <c r="A178" t="s">
         <v>351</v>
       </c>
@@ -20496,7 +20485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:31">
       <c r="A179" t="s">
         <v>352</v>
       </c>
@@ -20591,7 +20580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:31">
       <c r="A180" t="s">
         <v>353</v>
       </c>
@@ -20686,7 +20675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:31">
       <c r="A181" t="s">
         <v>354</v>
       </c>
@@ -20781,7 +20770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:31">
       <c r="A182" t="s">
         <v>355</v>
       </c>
@@ -20876,7 +20865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:31">
       <c r="A183" t="s">
         <v>356</v>
       </c>
@@ -20971,7 +20960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:31">
       <c r="A184" t="s">
         <v>357</v>
       </c>
@@ -21066,7 +21055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:31">
       <c r="A185" t="s">
         <v>358</v>
       </c>
@@ -21161,7 +21150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:31">
       <c r="A186" t="s">
         <v>359</v>
       </c>
@@ -21256,7 +21245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:31">
       <c r="A187" t="s">
         <v>360</v>
       </c>
@@ -21351,7 +21340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:31">
       <c r="A188" t="s">
         <v>361</v>
       </c>
@@ -21446,7 +21435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:31">
       <c r="A189" t="s">
         <v>362</v>
       </c>
@@ -21541,7 +21530,7 @@
         <v>95518500000000</v>
       </c>
     </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:31">
       <c r="A190" t="s">
         <v>363</v>
       </c>
@@ -21636,7 +21625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:31">
       <c r="A191" t="s">
         <v>364</v>
       </c>
@@ -21731,7 +21720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:31">
       <c r="A192" t="s">
         <v>365</v>
       </c>
@@ -21826,7 +21815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:31">
       <c r="A193" t="s">
         <v>366</v>
       </c>
@@ -21921,7 +21910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:31">
       <c r="A194" t="s">
         <v>367</v>
       </c>
@@ -22016,7 +22005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:31">
       <c r="A195" t="s">
         <v>368</v>
       </c>
@@ -22111,7 +22100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:31">
       <c r="A196" t="s">
         <v>369</v>
       </c>
@@ -22206,7 +22195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:31">
       <c r="A197" t="s">
         <v>370</v>
       </c>
@@ -22301,7 +22290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:31">
       <c r="A198" t="s">
         <v>371</v>
       </c>
@@ -22396,7 +22385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:31">
       <c r="A199" t="s">
         <v>372</v>
       </c>
@@ -22491,7 +22480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:31">
       <c r="A200" t="s">
         <v>373</v>
       </c>
@@ -22586,7 +22575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:31">
       <c r="A201" t="s">
         <v>374</v>
       </c>
@@ -22681,7 +22670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:31">
       <c r="A202" t="s">
         <v>375</v>
       </c>
@@ -22776,7 +22765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:31">
       <c r="A203" t="s">
         <v>376</v>
       </c>
@@ -22871,7 +22860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:31">
       <c r="A204" t="s">
         <v>377</v>
       </c>
@@ -22966,7 +22955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:31">
       <c r="A205" t="s">
         <v>378</v>
       </c>
@@ -23061,7 +23050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:31">
       <c r="A206" t="s">
         <v>379</v>
       </c>
@@ -23156,7 +23145,7 @@
         <v>2398450000</v>
       </c>
     </row>
-    <row r="207" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:31">
       <c r="A207" t="s">
         <v>380</v>
       </c>
@@ -23251,7 +23240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:31">
       <c r="A208" t="s">
         <v>381</v>
       </c>
@@ -23346,7 +23335,7 @@
         <v>338570000000</v>
       </c>
     </row>
-    <row r="209" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:31">
       <c r="A209" t="s">
         <v>382</v>
       </c>
@@ -23441,7 +23430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:31">
       <c r="A210" t="s">
         <v>383</v>
       </c>
@@ -23536,7 +23525,7 @@
         <v>21469000000</v>
       </c>
     </row>
-    <row r="211" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:31">
       <c r="A211" t="s">
         <v>384</v>
       </c>
@@ -23631,7 +23620,7 @@
         <v>10838400000</v>
       </c>
     </row>
-    <row r="212" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:31">
       <c r="A212" t="s">
         <v>385</v>
       </c>
@@ -23726,7 +23715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:31">
       <c r="A213" t="s">
         <v>386</v>
       </c>
@@ -23821,7 +23810,7 @@
         <v>1880500000000</v>
       </c>
     </row>
-    <row r="214" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:31">
       <c r="A214" t="s">
         <v>387</v>
       </c>
@@ -23916,7 +23905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:31">
       <c r="A215" t="s">
         <v>388</v>
       </c>
@@ -24011,7 +24000,7 @@
         <v>153739000000</v>
       </c>
     </row>
-    <row r="216" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:31">
       <c r="A216" t="s">
         <v>389</v>
       </c>
@@ -24106,7 +24095,7 @@
         <v>161615000</v>
       </c>
     </row>
-    <row r="217" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:31">
       <c r="A217" t="s">
         <v>390</v>
       </c>
@@ -24201,7 +24190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:31">
       <c r="A218" t="s">
         <v>391</v>
       </c>
@@ -24296,7 +24285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:31">
       <c r="A219" t="s">
         <v>392</v>
       </c>
@@ -24391,7 +24380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:31">
       <c r="A220" t="s">
         <v>393</v>
       </c>
@@ -24486,7 +24475,7 @@
         <v>9287170000</v>
       </c>
     </row>
-    <row r="221" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:31">
       <c r="A221" t="s">
         <v>394</v>
       </c>
@@ -24581,7 +24570,7 @@
         <v>517514</v>
       </c>
     </row>
-    <row r="222" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:31">
       <c r="A222" t="s">
         <v>395</v>
       </c>
@@ -24676,7 +24665,7 @@
         <v>2222210</v>
       </c>
     </row>
-    <row r="223" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:31">
       <c r="A223" t="s">
         <v>396</v>
       </c>
@@ -24771,7 +24760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:31">
       <c r="A224" t="s">
         <v>397</v>
       </c>
@@ -24866,7 +24855,7 @@
         <v>83436100</v>
       </c>
     </row>
-    <row r="225" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:31">
       <c r="A225" t="s">
         <v>398</v>
       </c>
@@ -24961,7 +24950,7 @@
         <v>46787300000</v>
       </c>
     </row>
-    <row r="226" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:31">
       <c r="A226" t="s">
         <v>399</v>
       </c>
@@ -25056,7 +25045,7 @@
         <v>26480300000</v>
       </c>
     </row>
-    <row r="227" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:31">
       <c r="A227" t="s">
         <v>400</v>
       </c>
@@ -25151,7 +25140,7 @@
         <v>33843400000</v>
       </c>
     </row>
-    <row r="228" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:31">
       <c r="A228" t="s">
         <v>401</v>
       </c>
@@ -25246,7 +25235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:31">
       <c r="A229" t="s">
         <v>402</v>
       </c>
@@ -25341,7 +25330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:31">
       <c r="A230" t="s">
         <v>403</v>
       </c>
@@ -25436,7 +25425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:31">
       <c r="A231" t="s">
         <v>404</v>
       </c>
@@ -25531,7 +25520,7 @@
         <v>6034760000000</v>
       </c>
     </row>
-    <row r="232" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:31">
       <c r="A232" t="s">
         <v>405</v>
       </c>
@@ -25626,7 +25615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:31">
       <c r="A233" t="s">
         <v>406</v>
       </c>
@@ -25721,7 +25710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:31">
       <c r="A234" t="s">
         <v>407</v>
       </c>
@@ -25816,7 +25805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:31">
       <c r="A235" t="s">
         <v>408</v>
       </c>
@@ -25911,7 +25900,7 @@
         <v>242521000000</v>
       </c>
     </row>
-    <row r="236" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:31">
       <c r="A236" t="s">
         <v>409</v>
       </c>
@@ -26006,7 +25995,7 @@
         <v>107125000000</v>
       </c>
     </row>
-    <row r="237" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:31">
       <c r="A237" t="s">
         <v>410</v>
       </c>
@@ -26101,7 +26090,7 @@
         <v>184319000000</v>
       </c>
     </row>
-    <row r="238" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:31">
       <c r="A238" t="s">
         <v>411</v>
       </c>
@@ -26196,7 +26185,7 @@
         <v>136687000000</v>
       </c>
     </row>
-    <row r="239" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:31">
       <c r="A239" t="s">
         <v>412</v>
       </c>
@@ -26291,7 +26280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:31">
       <c r="A240" t="s">
         <v>413</v>
       </c>
@@ -26386,7 +26375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:31">
       <c r="A241" t="s">
         <v>414</v>
       </c>
@@ -26481,7 +26470,7 @@
         <v>98336000000</v>
       </c>
     </row>
-    <row r="242" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:31">
       <c r="A242" t="s">
         <v>415</v>
       </c>
@@ -26576,7 +26565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:31">
       <c r="A243" t="s">
         <v>416</v>
       </c>
@@ -26671,7 +26660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:31">
       <c r="A244" t="s">
         <v>417</v>
       </c>
@@ -26766,7 +26755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:31">
       <c r="A245" t="s">
         <v>418</v>
       </c>
@@ -26861,7 +26850,7 @@
         <v>91821200000</v>
       </c>
     </row>
-    <row r="246" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:31">
       <c r="A246" t="s">
         <v>419</v>
       </c>
@@ -26956,7 +26945,7 @@
         <v>137978000000</v>
       </c>
     </row>
-    <row r="247" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:31">
       <c r="A247" t="s">
         <v>420</v>
       </c>
@@ -27051,7 +27040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:31">
       <c r="A248" t="s">
         <v>421</v>
       </c>
@@ -27146,7 +27135,7 @@
         <v>66376800000</v>
       </c>
     </row>
-    <row r="249" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:31">
       <c r="A249" t="s">
         <v>422</v>
       </c>
@@ -27241,7 +27230,7 @@
         <v>70556100000</v>
       </c>
     </row>
-    <row r="250" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:31">
       <c r="A250" t="s">
         <v>423</v>
       </c>
@@ -27336,7 +27325,7 @@
         <v>71170700000</v>
       </c>
     </row>
-    <row r="251" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:31">
       <c r="A251" t="s">
         <v>424</v>
       </c>
@@ -27431,7 +27420,7 @@
         <v>40293200000</v>
       </c>
     </row>
-    <row r="252" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:31">
       <c r="A252" t="s">
         <v>425</v>
       </c>
@@ -27526,7 +27515,7 @@
         <v>334588000000</v>
       </c>
     </row>
-    <row r="253" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:31">
       <c r="A253" t="s">
         <v>426</v>
       </c>
@@ -27621,7 +27610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:31">
       <c r="A254" t="s">
         <v>427</v>
       </c>
@@ -27716,7 +27705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:31">
       <c r="A255" t="s">
         <v>428</v>
       </c>
@@ -27811,7 +27800,7 @@
         <v>2105620000000</v>
       </c>
     </row>
-    <row r="256" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:31">
       <c r="A256" t="s">
         <v>429</v>
       </c>
@@ -27906,7 +27895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:31">
       <c r="A257" t="s">
         <v>430</v>
       </c>
@@ -28001,7 +27990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:31">
       <c r="A258" t="s">
         <v>431</v>
       </c>
@@ -28096,7 +28085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:31">
       <c r="A259" t="s">
         <v>432</v>
       </c>
@@ -28191,7 +28180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:31">
       <c r="A260" t="s">
         <v>433</v>
       </c>
@@ -28286,7 +28275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:31">
       <c r="A261" t="s">
         <v>434</v>
       </c>
@@ -28381,7 +28370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:31">
       <c r="A262" t="s">
         <v>435</v>
       </c>
@@ -28476,7 +28465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:31">
       <c r="A263" t="s">
         <v>436</v>
       </c>
@@ -28571,7 +28560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:31">
       <c r="A264" t="s">
         <v>437</v>
       </c>
@@ -28666,7 +28655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:31">
       <c r="A265" t="s">
         <v>438</v>
       </c>
@@ -28761,7 +28750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:31">
       <c r="A266" t="s">
         <v>439</v>
       </c>
@@ -28856,7 +28845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:31">
       <c r="A267" t="s">
         <v>440</v>
       </c>
@@ -28951,7 +28940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:31">
       <c r="A268" t="s">
         <v>441</v>
       </c>
@@ -29046,7 +29035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:31">
       <c r="A269" t="s">
         <v>442</v>
       </c>
@@ -29141,7 +29130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:31">
       <c r="A270" t="s">
         <v>443</v>
       </c>
@@ -29236,7 +29225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:31">
       <c r="A271" t="s">
         <v>444</v>
       </c>
@@ -29331,7 +29320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:31">
       <c r="A272" t="s">
         <v>445</v>
       </c>
@@ -29426,7 +29415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:31">
       <c r="A273" t="s">
         <v>446</v>
       </c>
@@ -29521,7 +29510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:31">
       <c r="A274" t="s">
         <v>447</v>
       </c>
@@ -29616,7 +29605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:31">
       <c r="A275" t="s">
         <v>448</v>
       </c>
@@ -29711,7 +29700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:31">
       <c r="A276" t="s">
         <v>449</v>
       </c>
@@ -29806,7 +29795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:31">
       <c r="A277" t="s">
         <v>450</v>
       </c>
@@ -29901,7 +29890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:31">
       <c r="A278" t="s">
         <v>451</v>
       </c>
@@ -29996,7 +29985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:31">
       <c r="A279" t="s">
         <v>452</v>
       </c>
@@ -30091,7 +30080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:31">
       <c r="A280" t="s">
         <v>453</v>
       </c>
@@ -30186,7 +30175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:31">
       <c r="B281" s="38"/>
       <c r="C281" s="38"/>
       <c r="D281" s="38"/>
@@ -30218,7 +30207,7 @@
       <c r="AD281" s="38"/>
       <c r="AE281" s="38"/>
     </row>
-    <row r="282" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:31">
       <c r="A282" t="s">
         <v>167</v>
       </c>
@@ -30343,7 +30332,7 @@
         <v>118453820000000</v>
       </c>
     </row>
-    <row r="283" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:31">
       <c r="B283" s="38"/>
       <c r="C283" s="38"/>
       <c r="D283" s="38"/>
@@ -30375,7 +30364,7 @@
       <c r="AD283" s="38"/>
       <c r="AE283" s="38"/>
     </row>
-    <row r="284" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:31">
       <c r="B284" s="38"/>
       <c r="C284" s="38"/>
       <c r="D284" s="38"/>
@@ -30407,7 +30396,7 @@
       <c r="AD284" s="38"/>
       <c r="AE284" s="38"/>
     </row>
-    <row r="285" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:31">
       <c r="B285" s="38"/>
       <c r="C285" s="38"/>
       <c r="D285" s="38"/>
@@ -30439,7 +30428,7 @@
       <c r="AD285" s="38"/>
       <c r="AE285" s="38"/>
     </row>
-    <row r="286" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:31">
       <c r="B286" s="38"/>
       <c r="C286" s="38"/>
       <c r="D286" s="38"/>
@@ -30471,7 +30460,7 @@
       <c r="AD286" s="38"/>
       <c r="AE286" s="38"/>
     </row>
-    <row r="287" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:31">
       <c r="B287" s="38"/>
       <c r="C287" s="38"/>
       <c r="D287" s="38"/>
@@ -30503,7 +30492,7 @@
       <c r="AD287" s="38"/>
       <c r="AE287" s="38"/>
     </row>
-    <row r="288" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:31">
       <c r="B288" s="38"/>
       <c r="C288" s="38"/>
       <c r="D288" s="38"/>
@@ -30535,7 +30524,7 @@
       <c r="AD288" s="38"/>
       <c r="AE288" s="38"/>
     </row>
-    <row r="289" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:31">
       <c r="B289" s="38"/>
       <c r="C289" s="38"/>
       <c r="D289" s="38"/>
@@ -30567,7 +30556,7 @@
       <c r="AD289" s="38"/>
       <c r="AE289" s="38"/>
     </row>
-    <row r="290" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:31">
       <c r="B290" s="38"/>
       <c r="C290" s="38"/>
       <c r="D290" s="38"/>
@@ -30599,7 +30588,7 @@
       <c r="AD290" s="38"/>
       <c r="AE290" s="38"/>
     </row>
-    <row r="293" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:31">
       <c r="B293" s="38"/>
       <c r="C293" s="38"/>
       <c r="D293" s="38"/>
@@ -30631,7 +30620,7 @@
       <c r="AD293" s="38"/>
       <c r="AE293" s="38"/>
     </row>
-    <row r="294" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:31">
       <c r="B294" s="38"/>
       <c r="C294" s="38"/>
       <c r="D294" s="38"/>
@@ -30663,7 +30652,7 @@
       <c r="AD294" s="38"/>
       <c r="AE294" s="38"/>
     </row>
-    <row r="295" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:31">
       <c r="B295" s="38"/>
       <c r="C295" s="38"/>
       <c r="D295" s="38"/>
@@ -30695,7 +30684,7 @@
       <c r="AD295" s="38"/>
       <c r="AE295" s="38"/>
     </row>
-    <row r="296" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:31">
       <c r="B296" s="38"/>
       <c r="C296" s="38"/>
       <c r="D296" s="38"/>
@@ -30727,7 +30716,7 @@
       <c r="AD296" s="38"/>
       <c r="AE296" s="38"/>
     </row>
-    <row r="297" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:31">
       <c r="B297" s="38"/>
       <c r="C297" s="38"/>
       <c r="D297" s="38"/>
@@ -30759,7 +30748,7 @@
       <c r="AD297" s="38"/>
       <c r="AE297" s="38"/>
     </row>
-    <row r="298" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:31">
       <c r="B298" s="38"/>
       <c r="C298" s="38"/>
       <c r="D298" s="38"/>
@@ -30791,7 +30780,7 @@
       <c r="AD298" s="38"/>
       <c r="AE298" s="38"/>
     </row>
-    <row r="299" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:31">
       <c r="B299" s="38"/>
       <c r="C299" s="38"/>
       <c r="D299" s="38"/>
@@ -30823,7 +30812,7 @@
       <c r="AD299" s="38"/>
       <c r="AE299" s="38"/>
     </row>
-    <row r="300" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:31">
       <c r="B300" s="38"/>
       <c r="C300" s="38"/>
       <c r="D300" s="38"/>
@@ -30867,14 +30856,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE26"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.875" customWidth="1"/>
+    <col min="1" max="1" width="44.90625" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31">
       <c r="A1" s="4" t="s">
         <v>170</v>
       </c>
@@ -30969,7 +30958,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -31064,7 +31053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -31159,7 +31148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -31254,7 +31243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -31349,7 +31338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -31444,7 +31433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -31539,7 +31528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -31634,7 +31623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -31729,132 +31718,102 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!B1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!B282</f>
         <v>0</v>
       </c>
       <c r="C10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!C1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!C282</f>
         <v>0</v>
       </c>
       <c r="D10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!D1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!D282</f>
         <v>0</v>
       </c>
       <c r="E10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!E1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!E282</f>
         <v>0</v>
       </c>
       <c r="F10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!F1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!F282</f>
         <v>0</v>
       </c>
       <c r="G10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!G1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!G282</f>
         <v>0</v>
       </c>
       <c r="H10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!H1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!H282</f>
         <v>0</v>
       </c>
       <c r="I10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!I1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!I282</f>
         <v>0</v>
       </c>
       <c r="J10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!J1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!J282</f>
         <v>0</v>
       </c>
       <c r="K10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!K1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!K282</f>
         <v>0</v>
       </c>
       <c r="L10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!L1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!L282</f>
-        <v>7.2509451221701132E-2</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!M1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!M282</f>
-        <v>0.14632284781067265</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!N1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!N282</f>
-        <v>0.22430075484895337</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!O1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!O282</f>
-        <v>0.30144254993781433</v>
-      </c>
-      <c r="P10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!P282</f>
-        <v>0.38143496250418402</v>
-      </c>
-      <c r="Q10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!Q282</f>
-        <v>0.38680033207566089</v>
-      </c>
-      <c r="R10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!R282</f>
-        <v>0.39213297034452449</v>
-      </c>
-      <c r="S10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!S282</f>
-        <v>0.39776118757096762</v>
-      </c>
-      <c r="T10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!T282</f>
-        <v>0.40116769069246927</v>
-      </c>
-      <c r="U10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!U282</f>
-        <v>0.40423294863096948</v>
-      </c>
-      <c r="V10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!V282</f>
-        <v>0.4066410742212464</v>
-      </c>
-      <c r="W10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!W282</f>
-        <v>0.40695687685312182</v>
-      </c>
-      <c r="X10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!X282</f>
-        <v>0.41190037995797696</v>
-      </c>
-      <c r="Y10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!Y282</f>
-        <v>0.41843989759215883</v>
-      </c>
-      <c r="Z10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!Z282</f>
-        <v>0.42562747195359713</v>
-      </c>
-      <c r="AA10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AA282</f>
-        <v>0.43504830369339176</v>
-      </c>
-      <c r="AB10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AB282</f>
-        <v>0.43798494442214675</v>
-      </c>
-      <c r="AC10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AC282</f>
-        <v>0.43361109650911933</v>
-      </c>
-      <c r="AD10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AD282</f>
-        <v>0.43598395826140429</v>
-      </c>
-      <c r="AE10" s="38">
-        <f>(MAX(TREND('Current and Planned Capacity'!$C$35:$D$35,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-energyEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12)/'BAU Emissions'!AE282</f>
-        <v>0.44217981007790547</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -31949,7 +31908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -32044,7 +32003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -32139,7 +32098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -32234,7 +32193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -32329,7 +32288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -32424,7 +32383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -32519,7 +32478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -32614,7 +32573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -32709,7 +32668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -32804,7 +32763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -32899,7 +32858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -32994,7 +32953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -33089,7 +33048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -33184,7 +33143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -33279,7 +33238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -33387,14 +33346,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE26"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.875" customWidth="1"/>
+    <col min="1" max="1" width="44.90625" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31">
       <c r="A1" s="4" t="s">
         <v>170</v>
       </c>
@@ -33489,7 +33448,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -33584,7 +33543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -33679,132 +33638,102 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B6</f>
-        <v>0.21472747612426446</v>
-      </c>
-      <c r="C4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C6</f>
-        <v>0.21508482860112188</v>
-      </c>
-      <c r="D4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D6</f>
-        <v>0.22069008404254345</v>
-      </c>
-      <c r="E4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E6</f>
-        <v>0.21979339457147218</v>
-      </c>
-      <c r="F4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F6</f>
-        <v>0.22908344617435641</v>
-      </c>
-      <c r="G4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G6</f>
-        <v>0.23331697478668498</v>
-      </c>
-      <c r="H4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H6</f>
-        <v>0.23408573257966597</v>
-      </c>
-      <c r="I4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I6</f>
-        <v>0.23374166379457553</v>
-      </c>
-      <c r="J4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J6</f>
-        <v>0.23266612915727847</v>
-      </c>
-      <c r="K4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K6</f>
-        <v>0.23394199621627729</v>
-      </c>
-      <c r="L4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L6</f>
-        <v>0.23540239523069187</v>
-      </c>
-      <c r="M4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M6</f>
-        <v>0.23791103389500834</v>
-      </c>
-      <c r="N4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N6</f>
-        <v>0.23966354205254939</v>
-      </c>
-      <c r="O4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O6</f>
-        <v>0.23899126345235353</v>
-      </c>
-      <c r="P4" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$29:$C$29,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P6</f>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="Q4" s="38">
-        <f>P4</f>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="R4" s="38">
-        <f t="shared" ref="R4:AE4" si="0">Q4</f>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="S4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="T4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="U4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="V4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="W4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="X4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="Y4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="Z4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="AA4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="AB4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="AC4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="AD4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-      <c r="AE4" s="38">
-        <f t="shared" si="0"/>
-        <v>0.23823611380356544</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -33899,7 +33828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -33994,7 +33923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -34089,7 +34018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -34184,7 +34113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -34279,132 +34208,102 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C12</f>
-        <v>1.7035952458279224E-2</v>
-      </c>
-      <c r="D10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D12</f>
-        <v>7.379540142338728E-2</v>
-      </c>
-      <c r="E10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E12</f>
-        <v>0.12978043460134511</v>
-      </c>
-      <c r="F10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F12</f>
-        <v>0.18340143676845078</v>
-      </c>
-      <c r="G10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G12</f>
-        <v>0.23726323944903455</v>
-      </c>
-      <c r="H10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H12</f>
-        <v>0.29179797708222832</v>
-      </c>
-      <c r="I10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I12</f>
-        <v>0.3465888690181968</v>
-      </c>
-      <c r="J10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$36:$C$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J12</f>
-        <v>0.40293807245549862</v>
-      </c>
-      <c r="K10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K12</f>
-        <v>0.46127828033038998</v>
-      </c>
-      <c r="L10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L12</f>
-        <v>0.46428938925855379</v>
-      </c>
-      <c r="M10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M12</f>
-        <v>0.46892634931043969</v>
-      </c>
-      <c r="N10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N12</f>
-        <v>0.47908528156881697</v>
-      </c>
-      <c r="O10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O12</f>
-        <v>0.48916293796855054</v>
-      </c>
-      <c r="P10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P12</f>
-        <v>0.49657659767289786</v>
-      </c>
-      <c r="Q10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Q12</f>
-        <v>0.50296540850885785</v>
-      </c>
-      <c r="R10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!R12</f>
-        <v>0.51456524577321661</v>
-      </c>
-      <c r="S10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!S12</f>
-        <v>0.52416240494873922</v>
-      </c>
-      <c r="T10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!T12</f>
-        <v>0.5337411036527685</v>
-      </c>
-      <c r="U10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!U12</f>
-        <v>0.54446206562073074</v>
-      </c>
-      <c r="V10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!V12</f>
-        <v>0.55091923685396671</v>
-      </c>
-      <c r="W10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!W12</f>
-        <v>0.55490684703794002</v>
-      </c>
-      <c r="X10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!X12</f>
-        <v>0.5637005765733456</v>
-      </c>
-      <c r="Y10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Y12</f>
-        <v>0.56928750459812449</v>
-      </c>
-      <c r="Z10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Z12</f>
-        <v>0.57880294177833458</v>
-      </c>
-      <c r="AA10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AA12</f>
-        <v>0.58666244942241519</v>
-      </c>
-      <c r="AB10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AB12</f>
-        <v>0.60164854466283457</v>
-      </c>
-      <c r="AC10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AC12</f>
-        <v>0.61282270980178088</v>
-      </c>
-      <c r="AD10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AD12</f>
-        <v>0.61033926350690149</v>
-      </c>
-      <c r="AE10" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$36:$D$36,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AE12</f>
-        <v>0.61297940852101807</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -34499,7 +34398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -34594,7 +34493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -34689,257 +34588,197 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B16</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C16</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D16</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E16</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F16</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G16</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H16</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I16</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J16</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$40:$C$40,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K16</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L16</f>
-        <v>0.12584183275816249</v>
-      </c>
-      <c r="M14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M16</f>
-        <v>0.24902718409452954</v>
-      </c>
-      <c r="N14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N16</f>
-        <v>0.37063322693604867</v>
-      </c>
-      <c r="O14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O16</f>
-        <v>0.49229651422155546</v>
-      </c>
-      <c r="P14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P16</f>
-        <v>0.61089208806394202</v>
-      </c>
-      <c r="Q14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Q16</f>
-        <v>0.60113262212048835</v>
-      </c>
-      <c r="R14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!R16</f>
-        <v>0.59361131092300634</v>
-      </c>
-      <c r="S14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!S16</f>
-        <v>0.58777591828937059</v>
-      </c>
-      <c r="T14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!T16</f>
-        <v>0.58158880336000873</v>
-      </c>
-      <c r="U14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!U16</f>
-        <v>0.57705234918255754</v>
-      </c>
-      <c r="V14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!V16</f>
-        <v>0.57101307812884161</v>
-      </c>
-      <c r="W14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!W16</f>
-        <v>0.56378506448164112</v>
-      </c>
-      <c r="X14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!X16</f>
-        <v>0.55816163289218235</v>
-      </c>
-      <c r="Y14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Y16</f>
-        <v>0.55553315123035074</v>
-      </c>
-      <c r="Z14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Z16</f>
-        <v>0.54979518443341302</v>
-      </c>
-      <c r="AA14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AA16</f>
-        <v>0.54349694548834093</v>
-      </c>
-      <c r="AB14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AB16</f>
-        <v>0.53853472784908896</v>
-      </c>
-      <c r="AC14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AC16</f>
-        <v>0.53346663031249886</v>
-      </c>
-      <c r="AD14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AD16</f>
-        <v>0.52939041470186365</v>
-      </c>
-      <c r="AE14" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$40:$D$40,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AE16</f>
-        <v>0.52524957511634962</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!B$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!B17</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!C$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!C17</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!D$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!D17</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!E$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!E17</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!F$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!F17</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!G$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!G17</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!H$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!H17</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!I$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!I17</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!J$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!J17</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$B$41:$C$41,'Current and Planned Capacity'!$B$26:$C$26,'BFoCPAbI-processEmis'!K$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!K17</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!L$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!L17</f>
-        <v>5.9126788165476771E-2</v>
-      </c>
-      <c r="M15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!M$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!M17</f>
-        <v>0.11856907216886765</v>
-      </c>
-      <c r="N15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!N$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!N17</f>
-        <v>0.17576472359261788</v>
-      </c>
-      <c r="O15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!O$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!O17</f>
-        <v>0.23485961304457414</v>
-      </c>
-      <c r="P15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!P17</f>
-        <v>0.29224072486387437</v>
-      </c>
-      <c r="Q15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Q17</f>
-        <v>0.29029708108805763</v>
-      </c>
-      <c r="R15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!R17</f>
-        <v>0.28995271918878357</v>
-      </c>
-      <c r="S15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!S17</f>
-        <v>0.28715947165900441</v>
-      </c>
-      <c r="T15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!T17</f>
-        <v>0.28468453561162887</v>
-      </c>
-      <c r="U15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!U17</f>
-        <v>0.28501649052722078</v>
-      </c>
-      <c r="V15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!V17</f>
-        <v>0.28310185577501101</v>
-      </c>
-      <c r="W15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!W17</f>
-        <v>0.27877525350837651</v>
-      </c>
-      <c r="X15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!X17</f>
-        <v>0.27669248616271735</v>
-      </c>
-      <c r="Y15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Y17</f>
-        <v>0.27625468159600419</v>
-      </c>
-      <c r="Z15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!Z17</f>
-        <v>0.27769841203833734</v>
-      </c>
-      <c r="AA15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AA17</f>
-        <v>0.27960437231313717</v>
-      </c>
-      <c r="AB15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AB17</f>
-        <v>0.28037410217497655</v>
-      </c>
-      <c r="AC15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AC17</f>
-        <v>0.28011705509528367</v>
-      </c>
-      <c r="AD15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AD17</f>
-        <v>0.27826746616136672</v>
-      </c>
-      <c r="AE15" s="38">
-        <f>MAX(TREND('Current and Planned Capacity'!$C$41:$D$41,'Current and Planned Capacity'!$C$26:$D$26,'BFoCPAbI-processEmis'!$P$1),0)*'Capacity Factor Data'!$A$45*10^12/'BAU Emissions'!AE17</f>
-        <v>0.27732033387354721</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -35034,7 +34873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -35129,7 +34968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -35224,7 +35063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -35319,7 +35158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -35414,7 +35253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -35509,7 +35348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -35604,7 +35443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -35699,7 +35538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -35794,7 +35633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -35889,7 +35728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -36136,18 +35975,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36169,18 +36008,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C87C9ED-B778-4193-A9C3-B7949AEFF542}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDA22ACB-0B36-444A-9EDB-569170CC84C9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C87C9ED-B778-4193-A9C3-B7949AEFF542}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>